--- a/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43935" yWindow="2685" windowWidth="36465" windowHeight="15450" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메인" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화목" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메인" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="월수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="화목" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\3.전산반배정\2.LMS전산반배정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903CAB08-316A-460E-A5CD-802DB42C5268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DB166C-8E50-49CB-BE2B-16494BD27B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9135" yWindow="3705" windowWidth="28860" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="메인" sheetId="1" r:id="rId1"/>
@@ -6275,8 +6275,8 @@
     <col min="14" max="15" width="9" style="2" customWidth="1"/>
     <col min="16" max="16" width="18.625" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="44.875" style="2" customWidth="1"/>
-    <col min="18" max="22" width="9" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="2"/>
+    <col min="18" max="26" width="9" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
@@ -11043,6 +11043,7 @@
       </c>
     </row>
     <row r="215" spans="1:13" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A215"/>
       <c r="B215" s="46"/>
       <c r="C215" s="6"/>
       <c r="K215" s="14" t="s">
@@ -11056,6 +11057,7 @@
       </c>
     </row>
     <row r="216" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A216"/>
       <c r="B216" s="46"/>
       <c r="C216" s="6"/>
       <c r="K216" s="14" t="s">
@@ -11069,6 +11071,7 @@
       </c>
     </row>
     <row r="217" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A217"/>
       <c r="B217" s="46"/>
       <c r="C217" s="6"/>
       <c r="K217" s="14" t="s">
@@ -11082,6 +11085,7 @@
       </c>
     </row>
     <row r="218" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A218"/>
       <c r="B218" s="46"/>
       <c r="C218" s="6"/>
       <c r="K218" s="14" t="s">
@@ -11095,6 +11099,7 @@
       </c>
     </row>
     <row r="219" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A219"/>
       <c r="B219" s="46"/>
       <c r="C219" s="6"/>
       <c r="K219" s="14" t="s">
@@ -11108,6 +11113,7 @@
       </c>
     </row>
     <row r="220" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A220"/>
       <c r="B220" s="47"/>
       <c r="C220" s="7"/>
       <c r="K220" s="14" t="s">
@@ -11121,6 +11127,7 @@
       </c>
     </row>
     <row r="221" spans="1:13" ht="18" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A221"/>
       <c r="B221" s="46"/>
       <c r="C221" s="6"/>
       <c r="K221" s="14" t="s">
@@ -11134,6 +11141,7 @@
       </c>
     </row>
     <row r="222" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A222"/>
       <c r="B222" s="46"/>
       <c r="C222" s="6"/>
       <c r="K222" s="14" t="s">
@@ -11147,6 +11155,7 @@
       </c>
     </row>
     <row r="223" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A223"/>
       <c r="B223" s="46"/>
       <c r="C223" s="6"/>
       <c r="K223" s="14" t="s">
@@ -11160,6 +11169,7 @@
       </c>
     </row>
     <row r="224" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A224"/>
       <c r="B224" s="46"/>
       <c r="C224" s="6"/>
       <c r="K224" s="14" t="s">
@@ -11173,6 +11183,7 @@
       </c>
     </row>
     <row r="225" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A225"/>
       <c r="B225" s="46"/>
       <c r="C225" s="6"/>
       <c r="K225" s="14" t="s">
@@ -11186,6 +11197,7 @@
       </c>
     </row>
     <row r="226" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A226"/>
       <c r="B226" s="47"/>
       <c r="C226" s="7"/>
       <c r="K226" s="14" t="s">
@@ -11199,6 +11211,7 @@
       </c>
     </row>
     <row r="227" spans="1:13" ht="18" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A227"/>
       <c r="B227" s="46"/>
       <c r="C227" s="6"/>
       <c r="K227" s="14" t="s">
@@ -11212,6 +11225,7 @@
       </c>
     </row>
     <row r="228" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A228"/>
       <c r="B228" s="46"/>
       <c r="C228" s="6"/>
       <c r="K228" s="14" t="s">
@@ -11225,6 +11239,7 @@
       </c>
     </row>
     <row r="229" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A229"/>
       <c r="B229" s="46"/>
       <c r="C229" s="6"/>
       <c r="K229" s="14" t="s">
@@ -11238,6 +11253,7 @@
       </c>
     </row>
     <row r="230" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A230"/>
       <c r="B230" s="46"/>
       <c r="C230" s="6"/>
       <c r="K230" s="14" t="s">
@@ -11251,6 +11267,7 @@
       </c>
     </row>
     <row r="231" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A231"/>
       <c r="B231" s="46"/>
       <c r="C231" s="6"/>
       <c r="K231" s="14" t="s">
@@ -11264,6 +11281,7 @@
       </c>
     </row>
     <row r="232" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A232"/>
       <c r="B232" s="47"/>
       <c r="C232" s="7"/>
       <c r="K232" s="14" t="s">
@@ -11277,6 +11295,7 @@
       </c>
     </row>
     <row r="233" spans="1:13" ht="18" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A233"/>
       <c r="B233" s="46"/>
       <c r="C233" s="6"/>
       <c r="K233" s="14" t="s">
@@ -11290,6 +11309,7 @@
       </c>
     </row>
     <row r="234" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A234"/>
       <c r="B234" s="46"/>
       <c r="C234" s="6"/>
       <c r="K234" s="14" t="s">
@@ -11303,6 +11323,7 @@
       </c>
     </row>
     <row r="235" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A235"/>
       <c r="B235" s="46"/>
       <c r="C235" s="6"/>
       <c r="K235" s="14" t="s">
@@ -11316,6 +11337,7 @@
       </c>
     </row>
     <row r="236" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A236"/>
       <c r="B236" s="46"/>
       <c r="C236" s="6"/>
       <c r="K236" s="14" t="s">
@@ -11329,6 +11351,7 @@
       </c>
     </row>
     <row r="237" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A237"/>
       <c r="B237" s="46"/>
       <c r="C237" s="6"/>
       <c r="K237" s="14" t="s">

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\3.전산반배정\2.LMS전산반배정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DB166C-8E50-49CB-BE2B-16494BD27B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACDB199-56EA-4C32-99E3-4139CA5874C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9135" yWindow="3705" windowWidth="28860" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36150" yWindow="4380" windowWidth="28860" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="메인" sheetId="1" r:id="rId1"/>
@@ -6275,8 +6275,8 @@
     <col min="14" max="15" width="9" style="2" customWidth="1"/>
     <col min="16" max="16" width="18.625" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="44.875" style="2" customWidth="1"/>
-    <col min="18" max="26" width="9" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="2"/>
+    <col min="18" max="25" width="9" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
@@ -17155,11 +17155,11 @@
     <mergeCell ref="B63:B68"/>
     <mergeCell ref="A93:A98"/>
     <mergeCell ref="A117:A121"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A75:A80"/>
-    <mergeCell ref="C9:C14"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="C75:C80"/>
     <mergeCell ref="A27:A32"/>
-    <mergeCell ref="C75:C80"/>
-    <mergeCell ref="B57:B62"/>
     <mergeCell ref="A21:A26"/>
     <mergeCell ref="C105:C110"/>
     <mergeCell ref="C21:C26"/>
@@ -22367,7 +22367,7 @@
     <mergeCell ref="C63:C68"/>
     <mergeCell ref="A99:A104"/>
     <mergeCell ref="C93:C98"/>
-    <mergeCell ref="A105:A109"/>
+    <mergeCell ref="C3:C8"/>
     <mergeCell ref="C105:C109"/>
     <mergeCell ref="A39:A44"/>
     <mergeCell ref="A15:A20"/>
@@ -22379,7 +22379,7 @@
     <mergeCell ref="C69:C74"/>
     <mergeCell ref="B75:B80"/>
     <mergeCell ref="A9:A14"/>
-    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="A105:A109"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/2.LMS전산반배정/LMS전산반배정.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="47595" yWindow="3795" windowWidth="28860" windowHeight="15465" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="31395" yWindow="3900" windowWidth="28860" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메인" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화목" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -140,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -428,19 +428,6 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
@@ -459,12 +446,14 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thick">
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -477,7 +466,9 @@
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -485,10 +476,10 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color rgb="FFCCCCCC"/>
       </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
@@ -508,22 +499,18 @@
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -548,32 +535,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -584,7 +545,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -729,7 +690,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -759,104 +720,38 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1255,11 +1150,11 @@
     <col width="9" customWidth="1" style="2" min="14" max="15"/>
     <col width="18.625" bestFit="1" customWidth="1" style="2" min="16" max="16"/>
     <col width="44.875" customWidth="1" style="2" min="17" max="17"/>
-    <col width="9" customWidth="1" style="2" min="18" max="27"/>
-    <col width="9" customWidth="1" style="2" min="28" max="16384"/>
+    <col width="9" customWidth="1" style="2" min="18" max="29"/>
+    <col width="9" customWidth="1" style="2" min="30" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="1" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B1" s="5" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1207,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="2" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1345,7 +1240,7 @@
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L2" s="0" t="inlineStr">
@@ -1369,7 +1264,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="3" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1402,7 +1297,7 @@
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L3" s="0" t="inlineStr">
@@ -1426,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="4" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1459,7 +1354,7 @@
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
@@ -1483,7 +1378,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="5" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1516,7 +1411,7 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
@@ -1538,7 +1433,7 @@
         <v>202510</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="6" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1571,7 +1466,7 @@
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
@@ -1593,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="7" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BG_MW_01</t>
@@ -1626,7 +1521,7 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
@@ -1650,7 +1545,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="8" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1683,7 +1578,7 @@
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
@@ -1697,7 +1592,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="9" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1730,7 +1625,7 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
@@ -1754,7 +1649,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="10" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1787,7 +1682,7 @@
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
@@ -1806,7 +1701,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="11" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1839,7 +1734,7 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">
@@ -1863,7 +1758,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="12" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1896,7 +1791,7 @@
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
@@ -1915,7 +1810,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="13" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>BG_MW_02</t>
@@ -1948,7 +1843,7 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
@@ -1967,7 +1862,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="14" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2000,7 +1895,7 @@
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
@@ -2014,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="15" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2047,7 +1942,7 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
@@ -2061,7 +1956,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="16" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2094,7 +1989,7 @@
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
@@ -2108,7 +2003,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="17" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2141,7 +2036,7 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
@@ -2155,7 +2050,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="18" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2188,7 +2083,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
@@ -2202,7 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="19" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t>BG_MW_03</t>
@@ -2235,7 +2130,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L19" s="0" t="inlineStr">
@@ -2249,7 +2144,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="20" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2282,7 +2177,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
@@ -2296,7 +2191,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="21" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2329,7 +2224,7 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
@@ -2343,7 +2238,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="22" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2376,7 +2271,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
@@ -2390,7 +2285,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="23" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2423,7 +2318,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
@@ -2437,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.25" customHeight="1" s="80" thickBot="1">
+    <row r="24" ht="29.25" customHeight="1" s="73" thickBot="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2470,7 +2365,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
@@ -2484,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="25" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>BG_MW_04</t>
@@ -2517,7 +2412,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L25" s="0" t="inlineStr">
@@ -2531,7 +2426,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="26" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2564,7 +2459,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
@@ -2578,7 +2473,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="27" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2611,7 +2506,7 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L27" s="0" t="inlineStr">
@@ -2625,7 +2520,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="28" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2658,7 +2553,7 @@
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L28" s="0" t="inlineStr">
@@ -2672,7 +2567,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="29" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2705,7 +2600,7 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
@@ -2719,7 +2614,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="30" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2752,7 +2647,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L30" s="0" t="inlineStr">
@@ -2766,7 +2661,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="31" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
           <t>BG_MW_05</t>
@@ -2799,7 +2694,7 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L31" s="0" t="inlineStr">
@@ -2813,7 +2708,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="32" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -2846,7 +2741,7 @@
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
@@ -2860,7 +2755,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="33" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -2893,7 +2788,7 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
@@ -2907,7 +2802,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="34" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -2940,7 +2835,7 @@
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -2954,7 +2849,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="35" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A35" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -2987,7 +2882,7 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
@@ -3001,7 +2896,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="36" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -3034,7 +2929,7 @@
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
@@ -3048,7 +2943,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="37" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A37" s="14" t="inlineStr">
         <is>
           <t>BG_MW_06</t>
@@ -3081,7 +2976,7 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
@@ -3095,7 +2990,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="38" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A38" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3116,7 +3011,7 @@
       <c r="H38" s="13" t="n"/>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
@@ -3130,7 +3025,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="39" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3150,7 +3045,7 @@
       <c r="H39" s="13" t="n"/>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L39" s="0" t="inlineStr">
@@ -3164,7 +3059,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="40" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3184,7 +3079,7 @@
       <c r="H40" s="13" t="n"/>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L40" s="0" t="inlineStr">
@@ -3198,7 +3093,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="41" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3218,7 +3113,7 @@
       <c r="H41" s="13" t="n"/>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L41" s="0" t="inlineStr">
@@ -3232,7 +3127,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="42" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3253,7 +3148,7 @@
       <c r="H42" s="13" t="n"/>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L42" s="0" t="inlineStr">
@@ -3267,7 +3162,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="43" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
           <t>BG_MW_07</t>
@@ -3288,7 +3183,7 @@
       <c r="H43" s="13" t="n"/>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L43" s="0" t="inlineStr">
@@ -3302,7 +3197,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="44" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
           <t>BG_MW_08</t>
@@ -3323,7 +3218,7 @@
       <c r="H44" s="13" t="n"/>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L44" s="0" t="inlineStr">
@@ -3337,7 +3232,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="45" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
           <t>BG_MW_08</t>
@@ -3358,7 +3253,7 @@
       <c r="H45" s="13" t="n"/>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L45" s="0" t="inlineStr">
@@ -3372,7 +3267,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="46" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
           <t>BG_MW_08</t>
@@ -3393,7 +3288,7 @@
       <c r="H46" s="13" t="n"/>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L46" s="0" t="inlineStr">
@@ -3407,7 +3302,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="47" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
           <t>BG_MW_08</t>
@@ -3428,7 +3323,7 @@
       <c r="H47" s="13" t="n"/>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>BG_TT_20</t>
+          <t>BG_MW_18</t>
         </is>
       </c>
       <c r="L47" s="0" t="inlineStr">
@@ -3442,7 +3337,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="48" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
           <t>BG_MW_08</t>
@@ -3477,7 +3372,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="49" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>BG_MW_09</t>
@@ -3512,7 +3407,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="50" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
           <t>BG_MW_09</t>
@@ -3547,7 +3442,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="51" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
           <t>BG_MW_09</t>
@@ -3582,7 +3477,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="52" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
           <t>BG_MW_09</t>
@@ -3617,7 +3512,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="53" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
           <t>BG_MW_09</t>
@@ -3652,7 +3547,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="54" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3687,7 +3582,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="55" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3722,7 +3617,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="56" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3757,7 +3652,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="57" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3792,7 +3687,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="58" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3827,7 +3722,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="59" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
           <t>BG_MW_10</t>
@@ -3862,7 +3757,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="60" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -3897,7 +3792,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="61" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A61" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -3932,7 +3827,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="62" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -3967,7 +3862,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="63" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -4002,7 +3897,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="64" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -4037,7 +3932,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="65" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A65" s="14" t="inlineStr">
         <is>
           <t>BG_MW_11</t>
@@ -4072,7 +3967,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="66" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4106,7 +4001,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="67" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4140,7 +4035,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="68" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4174,7 +4069,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="69" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4208,7 +4103,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="70" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4242,7 +4137,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="71" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>BG_MW_12</t>
@@ -4276,7 +4171,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="72" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>BG_MW_13</t>
@@ -4310,7 +4205,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="73" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>BG_MW_13</t>
@@ -4342,7 +4237,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="74" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>BG_MW_13</t>
@@ -4374,7 +4269,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="75" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>BG_MW_13</t>
@@ -4406,7 +4301,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="76" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
           <t>BG_MW_13</t>
@@ -4438,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="77" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4470,7 +4365,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="78" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4502,7 +4397,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="79" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A79" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4534,7 +4429,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="80" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A80" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4566,7 +4461,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="81" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A81" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4598,7 +4493,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="82" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A82" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4630,7 +4525,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="83" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A83" s="14" t="inlineStr">
         <is>
           <t>BG_MW_14</t>
@@ -4662,7 +4557,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="84" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A84" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4694,7 +4589,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="85" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A85" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4726,7 +4621,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="86" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A86" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4758,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="87" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A87" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4790,7 +4685,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="88" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A88" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4822,7 +4717,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="89" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A89" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4854,7 +4749,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="90" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A90" s="14" t="inlineStr">
         <is>
           <t>BG_MW_15</t>
@@ -4886,7 +4781,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="91" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A91" s="14" t="inlineStr">
         <is>
           <t>BG_MW_16</t>
@@ -4918,7 +4813,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="92" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A92" s="14" t="inlineStr">
         <is>
           <t>BG_MW_16</t>
@@ -4950,7 +4845,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="93" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A93" s="14" t="inlineStr">
         <is>
           <t>BG_MW_16</t>
@@ -4970,7 +4865,7 @@
       <c r="L93" s="12" t="n"/>
       <c r="M93" s="13" t="n"/>
     </row>
-    <row r="94" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="94" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A94" s="14" t="inlineStr">
         <is>
           <t>BG_MW_16</t>
@@ -4990,7 +4885,7 @@
       <c r="L94" s="12" t="n"/>
       <c r="M94" s="13" t="n"/>
     </row>
-    <row r="95" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="95" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A95" s="14" t="inlineStr">
         <is>
           <t>BG_MW_17</t>
@@ -5010,7 +4905,7 @@
       <c r="L95" s="12" t="n"/>
       <c r="M95" s="13" t="n"/>
     </row>
-    <row r="96" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="96" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A96" s="14" t="inlineStr">
         <is>
           <t>BG_MW_17</t>
@@ -5030,7 +4925,7 @@
       <c r="L96" s="12" t="n"/>
       <c r="M96" s="13" t="n"/>
     </row>
-    <row r="97" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="97" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A97" s="14" t="inlineStr">
         <is>
           <t>BG_MW_17</t>
@@ -5050,7 +4945,7 @@
       <c r="L97" s="12" t="n"/>
       <c r="M97" s="13" t="n"/>
     </row>
-    <row r="98" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="98" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A98" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5070,7 +4965,7 @@
       <c r="L98" s="12" t="n"/>
       <c r="M98" s="13" t="n"/>
     </row>
-    <row r="99" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="99" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A99" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5090,7 +4985,7 @@
       <c r="L99" s="12" t="n"/>
       <c r="M99" s="13" t="n"/>
     </row>
-    <row r="100" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="100" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A100" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5110,7 +5005,7 @@
       <c r="L100" s="12" t="n"/>
       <c r="M100" s="13" t="n"/>
     </row>
-    <row r="101" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="101" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A101" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5130,7 +5025,7 @@
       <c r="L101" s="12" t="n"/>
       <c r="M101" s="13" t="n"/>
     </row>
-    <row r="102" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="102" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A102" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5150,7 +5045,7 @@
       <c r="L102" s="12" t="n"/>
       <c r="M102" s="13" t="n"/>
     </row>
-    <row r="103" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="103" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A103" s="14" t="inlineStr">
         <is>
           <t>BG_TT_01</t>
@@ -5170,7 +5065,7 @@
       <c r="L103" s="12" t="n"/>
       <c r="M103" s="13" t="n"/>
     </row>
-    <row r="104" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="104" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A104" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5190,7 +5085,7 @@
       <c r="L104" s="12" t="n"/>
       <c r="M104" s="13" t="n"/>
     </row>
-    <row r="105" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="105" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A105" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5210,7 +5105,7 @@
       <c r="L105" s="12" t="n"/>
       <c r="M105" s="13" t="n"/>
     </row>
-    <row r="106" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="106" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A106" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5230,7 +5125,7 @@
       <c r="L106" s="12" t="n"/>
       <c r="M106" s="13" t="n"/>
     </row>
-    <row r="107" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="107" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A107" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5250,7 +5145,7 @@
       <c r="L107" s="12" t="n"/>
       <c r="M107" s="13" t="n"/>
     </row>
-    <row r="108" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="108" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A108" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5270,7 +5165,7 @@
       <c r="L108" s="12" t="n"/>
       <c r="M108" s="13" t="n"/>
     </row>
-    <row r="109" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="109" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A109" s="14" t="inlineStr">
         <is>
           <t>BG_TT_02</t>
@@ -5290,7 +5185,7 @@
       <c r="L109" s="12" t="n"/>
       <c r="M109" s="13" t="n"/>
     </row>
-    <row r="110" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="110" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A110" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5310,7 +5205,7 @@
       <c r="L110" s="12" t="n"/>
       <c r="M110" s="13" t="n"/>
     </row>
-    <row r="111" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="111" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A111" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5330,7 +5225,7 @@
       <c r="L111" s="12" t="n"/>
       <c r="M111" s="13" t="n"/>
     </row>
-    <row r="112" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="112" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A112" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5350,7 +5245,7 @@
       <c r="L112" s="12" t="n"/>
       <c r="M112" s="13" t="n"/>
     </row>
-    <row r="113" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="113" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A113" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5370,7 +5265,7 @@
       <c r="L113" s="12" t="n"/>
       <c r="M113" s="13" t="n"/>
     </row>
-    <row r="114" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="114" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A114" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5390,7 +5285,7 @@
       <c r="L114" s="12" t="n"/>
       <c r="M114" s="13" t="n"/>
     </row>
-    <row r="115" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="115" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A115" s="14" t="inlineStr">
         <is>
           <t>BG_TT_03</t>
@@ -5410,7 +5305,7 @@
       <c r="L115" s="12" t="n"/>
       <c r="M115" s="13" t="n"/>
     </row>
-    <row r="116" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="116" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A116" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5430,7 +5325,7 @@
       <c r="L116" s="12" t="n"/>
       <c r="M116" s="13" t="n"/>
     </row>
-    <row r="117" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="117" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5450,7 +5345,7 @@
       <c r="L117" s="12" t="n"/>
       <c r="M117" s="13" t="n"/>
     </row>
-    <row r="118" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="118" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A118" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5470,7 +5365,7 @@
       <c r="L118" s="12" t="n"/>
       <c r="M118" s="13" t="n"/>
     </row>
-    <row r="119" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="119" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A119" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5490,7 +5385,7 @@
       <c r="L119" s="12" t="n"/>
       <c r="M119" s="13" t="n"/>
     </row>
-    <row r="120" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="120" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A120" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5510,7 +5405,7 @@
       <c r="L120" s="12" t="n"/>
       <c r="M120" s="13" t="n"/>
     </row>
-    <row r="121" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="121" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A121" s="14" t="inlineStr">
         <is>
           <t>BG_TT_04</t>
@@ -5530,7 +5425,7 @@
       <c r="L121" s="12" t="n"/>
       <c r="M121" s="13" t="n"/>
     </row>
-    <row r="122" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="122" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A122" s="14" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5550,7 +5445,7 @@
       <c r="L122" s="12" t="n"/>
       <c r="M122" s="13" t="n"/>
     </row>
-    <row r="123" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="123" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A123" s="14" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5570,7 +5465,7 @@
       <c r="L123" s="12" t="n"/>
       <c r="M123" s="13" t="n"/>
     </row>
-    <row r="124" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="124" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A124" s="14" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5590,7 +5485,7 @@
       <c r="L124" s="12" t="n"/>
       <c r="M124" s="13" t="n"/>
     </row>
-    <row r="125" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="125" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A125" s="0" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5610,7 +5505,7 @@
       <c r="L125" s="12" t="n"/>
       <c r="M125" s="13" t="n"/>
     </row>
-    <row r="126" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="126" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A126" s="0" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5630,7 +5525,7 @@
       <c r="L126" s="12" t="n"/>
       <c r="M126" s="13" t="n"/>
     </row>
-    <row r="127" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="127" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A127" s="0" t="inlineStr">
         <is>
           <t>BG_TT_05</t>
@@ -5650,7 +5545,7 @@
       <c r="L127" s="12" t="n"/>
       <c r="M127" s="13" t="n"/>
     </row>
-    <row r="128" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="128" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A128" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5670,7 +5565,7 @@
       <c r="L128" s="12" t="n"/>
       <c r="M128" s="13" t="n"/>
     </row>
-    <row r="129" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="129" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A129" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5690,7 +5585,7 @@
       <c r="L129" s="12" t="n"/>
       <c r="M129" s="13" t="n"/>
     </row>
-    <row r="130" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="130" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A130" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5710,7 +5605,7 @@
       <c r="L130" s="12" t="n"/>
       <c r="M130" s="13" t="n"/>
     </row>
-    <row r="131" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="131" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A131" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5730,7 +5625,7 @@
       <c r="L131" s="12" t="n"/>
       <c r="M131" s="13" t="n"/>
     </row>
-    <row r="132" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="132" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A132" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5750,7 +5645,7 @@
       <c r="L132" s="12" t="n"/>
       <c r="M132" s="13" t="n"/>
     </row>
-    <row r="133" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="133" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A133" s="0" t="inlineStr">
         <is>
           <t>BG_TT_06</t>
@@ -5770,7 +5665,7 @@
       <c r="L133" s="12" t="n"/>
       <c r="M133" s="13" t="n"/>
     </row>
-    <row r="134" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="134" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A134" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5790,7 +5685,7 @@
       <c r="L134" s="12" t="n"/>
       <c r="M134" s="13" t="n"/>
     </row>
-    <row r="135" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="135" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A135" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5810,7 +5705,7 @@
       <c r="L135" s="12" t="n"/>
       <c r="M135" s="13" t="n"/>
     </row>
-    <row r="136" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="136" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A136" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5830,7 +5725,7 @@
       <c r="L136" s="12" t="n"/>
       <c r="M136" s="13" t="n"/>
     </row>
-    <row r="137" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="137" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A137" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5850,7 +5745,7 @@
       <c r="L137" s="12" t="n"/>
       <c r="M137" s="13" t="n"/>
     </row>
-    <row r="138" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="138" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A138" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5870,7 +5765,7 @@
       <c r="L138" s="12" t="n"/>
       <c r="M138" s="13" t="n"/>
     </row>
-    <row r="139" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="139" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A139" s="0" t="inlineStr">
         <is>
           <t>BG_TT_07</t>
@@ -5890,7 +5785,7 @@
       <c r="L139" s="12" t="n"/>
       <c r="M139" s="13" t="n"/>
     </row>
-    <row r="140" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="140" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A140" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -5910,7 +5805,7 @@
       <c r="L140" s="12" t="n"/>
       <c r="M140" s="13" t="n"/>
     </row>
-    <row r="141" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="141" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A141" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -5930,7 +5825,7 @@
       <c r="L141" s="12" t="n"/>
       <c r="M141" s="13" t="n"/>
     </row>
-    <row r="142" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="142" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A142" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -5950,7 +5845,7 @@
       <c r="L142" s="12" t="n"/>
       <c r="M142" s="13" t="n"/>
     </row>
-    <row r="143" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="143" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A143" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -5970,7 +5865,7 @@
       <c r="L143" s="12" t="n"/>
       <c r="M143" s="13" t="n"/>
     </row>
-    <row r="144" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="144" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A144" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -5990,7 +5885,7 @@
       <c r="L144" s="12" t="n"/>
       <c r="M144" s="13" t="n"/>
     </row>
-    <row r="145" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="145" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A145" s="0" t="inlineStr">
         <is>
           <t>BG_TT_08</t>
@@ -6010,7 +5905,7 @@
       <c r="L145" s="12" t="n"/>
       <c r="M145" s="13" t="n"/>
     </row>
-    <row r="146" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="146" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A146" s="14" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6030,7 +5925,7 @@
       <c r="L146" s="12" t="n"/>
       <c r="M146" s="13" t="n"/>
     </row>
-    <row r="147" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="147" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A147" s="14" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6050,7 +5945,7 @@
       <c r="L147" s="12" t="n"/>
       <c r="M147" s="13" t="n"/>
     </row>
-    <row r="148" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="148" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A148" s="14" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6070,7 +5965,7 @@
       <c r="L148" s="12" t="n"/>
       <c r="M148" s="13" t="n"/>
     </row>
-    <row r="149" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="149" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A149" s="0" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6090,7 +5985,7 @@
       <c r="L149" s="12" t="n"/>
       <c r="M149" s="13" t="n"/>
     </row>
-    <row r="150" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="150" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A150" s="0" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6110,7 +6005,7 @@
       <c r="L150" s="12" t="n"/>
       <c r="M150" s="13" t="n"/>
     </row>
-    <row r="151" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="151" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A151" s="0" t="inlineStr">
         <is>
           <t>BG_TT_09</t>
@@ -6130,7 +6025,7 @@
       <c r="L151" s="12" t="n"/>
       <c r="M151" s="13" t="n"/>
     </row>
-    <row r="152" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="152" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A152" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6150,7 +6045,7 @@
       <c r="L152" s="12" t="n"/>
       <c r="M152" s="13" t="n"/>
     </row>
-    <row r="153" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="153" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A153" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6170,7 +6065,7 @@
       <c r="L153" s="12" t="n"/>
       <c r="M153" s="13" t="n"/>
     </row>
-    <row r="154" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="154" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A154" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6190,7 +6085,7 @@
       <c r="L154" s="12" t="n"/>
       <c r="M154" s="13" t="n"/>
     </row>
-    <row r="155" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="155" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A155" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6210,7 +6105,7 @@
       <c r="L155" s="12" t="n"/>
       <c r="M155" s="13" t="n"/>
     </row>
-    <row r="156" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="156" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A156" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6230,7 +6125,7 @@
       <c r="L156" s="12" t="n"/>
       <c r="M156" s="13" t="n"/>
     </row>
-    <row r="157" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="157" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A157" s="0" t="inlineStr">
         <is>
           <t>BG_TT_10</t>
@@ -6250,7 +6145,7 @@
       <c r="L157" s="12" t="n"/>
       <c r="M157" s="13" t="n"/>
     </row>
-    <row r="158" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="158" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A158" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6270,7 +6165,7 @@
       <c r="L158" s="12" t="n"/>
       <c r="M158" s="13" t="n"/>
     </row>
-    <row r="159" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="159" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A159" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6290,7 +6185,7 @@
       <c r="L159" s="12" t="n"/>
       <c r="M159" s="13" t="n"/>
     </row>
-    <row r="160" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="160" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A160" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6310,7 +6205,7 @@
       <c r="L160" s="12" t="n"/>
       <c r="M160" s="13" t="n"/>
     </row>
-    <row r="161" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="161" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A161" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6330,7 +6225,7 @@
       <c r="L161" s="12" t="n"/>
       <c r="M161" s="13" t="n"/>
     </row>
-    <row r="162" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="162" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A162" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6350,7 +6245,7 @@
       <c r="L162" s="12" t="n"/>
       <c r="M162" s="13" t="n"/>
     </row>
-    <row r="163" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="163" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A163" s="0" t="inlineStr">
         <is>
           <t>BG_TT_11</t>
@@ -6370,7 +6265,7 @@
       <c r="L163" s="12" t="n"/>
       <c r="M163" s="13" t="n"/>
     </row>
-    <row r="164" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="164" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A164" s="0" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6390,7 +6285,7 @@
       <c r="L164" s="12" t="n"/>
       <c r="M164" s="13" t="n"/>
     </row>
-    <row r="165" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="165" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A165" s="0" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6410,7 +6305,7 @@
       <c r="L165" s="12" t="n"/>
       <c r="M165" s="13" t="n"/>
     </row>
-    <row r="166" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="166" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A166" s="0" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6430,7 +6325,7 @@
       <c r="L166" s="12" t="n"/>
       <c r="M166" s="13" t="n"/>
     </row>
-    <row r="167" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="167" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A167" s="0" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6450,7 +6345,7 @@
       <c r="L167" s="12" t="n"/>
       <c r="M167" s="13" t="n"/>
     </row>
-    <row r="168" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="168" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A168" s="0" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6470,7 +6365,7 @@
       <c r="L168" s="12" t="n"/>
       <c r="M168" s="13" t="n"/>
     </row>
-    <row r="169" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="169" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A169" s="14" t="inlineStr">
         <is>
           <t>BG_TT_12</t>
@@ -6490,7 +6385,7 @@
       <c r="L169" s="12" t="n"/>
       <c r="M169" s="13" t="n"/>
     </row>
-    <row r="170" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="170" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A170" s="14" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6510,7 +6405,7 @@
       <c r="L170" s="12" t="n"/>
       <c r="M170" s="13" t="n"/>
     </row>
-    <row r="171" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="171" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A171" s="14" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6530,7 +6425,7 @@
       <c r="L171" s="12" t="n"/>
       <c r="M171" s="13" t="n"/>
     </row>
-    <row r="172" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="172" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A172" s="0" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6550,7 +6445,7 @@
       <c r="L172" s="12" t="n"/>
       <c r="M172" s="13" t="n"/>
     </row>
-    <row r="173" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="173" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A173" s="0" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6570,7 +6465,7 @@
       <c r="L173" s="12" t="n"/>
       <c r="M173" s="13" t="n"/>
     </row>
-    <row r="174" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="174" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A174" s="0" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6590,7 +6485,7 @@
       <c r="L174" s="12" t="n"/>
       <c r="M174" s="13" t="n"/>
     </row>
-    <row r="175" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="175" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A175" s="0" t="inlineStr">
         <is>
           <t>BG_TT_13</t>
@@ -6610,7 +6505,7 @@
       <c r="L175" s="12" t="n"/>
       <c r="M175" s="13" t="n"/>
     </row>
-    <row r="176" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="176" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A176" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6630,7 +6525,7 @@
       <c r="L176" s="12" t="n"/>
       <c r="M176" s="13" t="n"/>
     </row>
-    <row r="177" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="177" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A177" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6650,7 +6545,7 @@
       <c r="L177" s="12" t="n"/>
       <c r="M177" s="13" t="n"/>
     </row>
-    <row r="178" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="178" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A178" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6670,7 +6565,7 @@
       <c r="L178" s="12" t="n"/>
       <c r="M178" s="13" t="n"/>
     </row>
-    <row r="179" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="179" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A179" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6690,7 +6585,7 @@
       <c r="L179" s="12" t="n"/>
       <c r="M179" s="13" t="n"/>
     </row>
-    <row r="180" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="180" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A180" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6710,7 +6605,7 @@
       <c r="L180" s="12" t="n"/>
       <c r="M180" s="13" t="n"/>
     </row>
-    <row r="181" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="181" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A181" s="0" t="inlineStr">
         <is>
           <t>BG_TT_14</t>
@@ -6730,7 +6625,7 @@
       <c r="L181" s="12" t="n"/>
       <c r="M181" s="13" t="n"/>
     </row>
-    <row r="182" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="182" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A182" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6750,7 +6645,7 @@
       <c r="L182" s="12" t="n"/>
       <c r="M182" s="13" t="n"/>
     </row>
-    <row r="183" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="183" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A183" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6768,7 +6663,7 @@
       </c>
       <c r="K183" s="14" t="n"/>
     </row>
-    <row r="184" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="184" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A184" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6786,7 +6681,7 @@
       </c>
       <c r="K184" s="14" t="n"/>
     </row>
-    <row r="185" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="185" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A185" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6804,7 +6699,7 @@
       </c>
       <c r="K185" s="14" t="n"/>
     </row>
-    <row r="186" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="186" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A186" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6822,7 +6717,7 @@
       </c>
       <c r="K186" s="14" t="n"/>
     </row>
-    <row r="187" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="187" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A187" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6840,7 +6735,7 @@
       </c>
       <c r="K187" s="14" t="n"/>
     </row>
-    <row r="188" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="188" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A188" s="0" t="inlineStr">
         <is>
           <t>BG_TT_15</t>
@@ -6858,7 +6753,7 @@
       </c>
       <c r="K188" s="14" t="n"/>
     </row>
-    <row r="189" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="189" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A189" s="0" t="inlineStr">
         <is>
           <t>BG_TT_16</t>
@@ -6876,7 +6771,7 @@
       </c>
       <c r="K189" s="14" t="n"/>
     </row>
-    <row r="190" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="190" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A190" s="0" t="inlineStr">
         <is>
           <t>BG_TT_16</t>
@@ -6894,7 +6789,7 @@
       </c>
       <c r="K190" s="14" t="n"/>
     </row>
-    <row r="191" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="191" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A191" s="0" t="inlineStr">
         <is>
           <t>BG_TT_16</t>
@@ -6912,7 +6807,7 @@
       </c>
       <c r="K191" s="14" t="n"/>
     </row>
-    <row r="192" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="192" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A192" s="14" t="inlineStr">
         <is>
           <t>BG_TT_16</t>
@@ -6930,7 +6825,7 @@
       </c>
       <c r="K192" s="14" t="n"/>
     </row>
-    <row r="193" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="193" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A193" s="14" t="inlineStr">
         <is>
           <t>BG_TT_16</t>
@@ -6948,7 +6843,7 @@
       </c>
       <c r="K193" s="14" t="n"/>
     </row>
-    <row r="194" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="194" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A194" s="14" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -6966,7 +6861,7 @@
       </c>
       <c r="K194" s="14" t="n"/>
     </row>
-    <row r="195" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="195" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A195" s="0" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -6984,7 +6879,7 @@
       </c>
       <c r="K195" s="14" t="n"/>
     </row>
-    <row r="196" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="196" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A196" s="0" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -7002,7 +6897,7 @@
       </c>
       <c r="K196" s="14" t="n"/>
     </row>
-    <row r="197" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="197" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A197" s="0" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -7020,7 +6915,7 @@
       </c>
       <c r="K197" s="14" t="n"/>
     </row>
-    <row r="198" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="198" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A198" s="0" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -7038,7 +6933,7 @@
       </c>
       <c r="K198" s="14" t="n"/>
     </row>
-    <row r="199" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="199" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A199" s="0" t="inlineStr">
         <is>
           <t>BG_TT_17</t>
@@ -7056,7 +6951,7 @@
       </c>
       <c r="K199" s="14" t="n"/>
     </row>
-    <row r="200" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="200" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A200" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7074,7 +6969,7 @@
       </c>
       <c r="K200" s="14" t="n"/>
     </row>
-    <row r="201" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="201" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A201" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7092,7 +6987,7 @@
       </c>
       <c r="K201" s="14" t="n"/>
     </row>
-    <row r="202" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="202" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A202" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7110,7 +7005,7 @@
       </c>
       <c r="K202" s="14" t="n"/>
     </row>
-    <row r="203" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="203" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A203" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7128,7 +7023,7 @@
       </c>
       <c r="K203" s="14" t="n"/>
     </row>
-    <row r="204" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="204" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A204" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7146,7 +7041,7 @@
       </c>
       <c r="K204" s="14" t="n"/>
     </row>
-    <row r="205" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="205" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A205" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7164,7 +7059,7 @@
       </c>
       <c r="K205" s="14" t="n"/>
     </row>
-    <row r="206" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="206" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A206" s="0" t="inlineStr">
         <is>
           <t>BG_TT_18</t>
@@ -7182,7 +7077,7 @@
       </c>
       <c r="K206" s="14" t="n"/>
     </row>
-    <row r="207" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="207" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A207" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7200,7 +7095,7 @@
       </c>
       <c r="K207" s="14" t="n"/>
     </row>
-    <row r="208" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="208" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A208" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7218,7 +7113,7 @@
       </c>
       <c r="K208" s="14" t="n"/>
     </row>
-    <row r="209" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="209" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A209" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7236,7 +7131,7 @@
       </c>
       <c r="K209" s="14" t="n"/>
     </row>
-    <row r="210" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="210" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A210" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7254,7 +7149,7 @@
       </c>
       <c r="K210" s="14" t="n"/>
     </row>
-    <row r="211" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="211" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A211" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7272,7 +7167,7 @@
       </c>
       <c r="K211" s="14" t="n"/>
     </row>
-    <row r="212" ht="18" customHeight="1" s="80" thickBot="1">
+    <row r="212" ht="18" customHeight="1" s="73" thickBot="1">
       <c r="A212" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7290,7 +7185,7 @@
       </c>
       <c r="K212" s="14" t="n"/>
     </row>
-    <row r="213" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="213" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A213" s="0" t="inlineStr">
         <is>
           <t>BG_TT_19</t>
@@ -7308,483 +7203,483 @@
       </c>
       <c r="K213" s="14" t="n"/>
     </row>
-    <row r="214" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="214" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A214" s="0" t="n"/>
       <c r="B214" s="39" t="n"/>
       <c r="C214" s="7" t="n"/>
       <c r="K214" s="14" t="n"/>
     </row>
-    <row r="215" ht="17.25" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="215" ht="17.25" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A215" s="0" t="n"/>
       <c r="B215" s="38" t="n"/>
       <c r="C215" s="6" t="n"/>
       <c r="K215" s="14" t="n"/>
     </row>
-    <row r="216" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="216" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A216" s="0" t="n"/>
       <c r="B216" s="38" t="n"/>
       <c r="C216" s="6" t="n"/>
       <c r="K216" s="14" t="n"/>
     </row>
-    <row r="217" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="217" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A217" s="0" t="n"/>
       <c r="B217" s="38" t="n"/>
       <c r="C217" s="6" t="n"/>
       <c r="K217" s="14" t="n"/>
     </row>
-    <row r="218" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="218" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A218" s="0" t="n"/>
       <c r="B218" s="38" t="n"/>
       <c r="C218" s="6" t="n"/>
       <c r="K218" s="14" t="n"/>
     </row>
-    <row r="219" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="219" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A219" s="0" t="n"/>
       <c r="B219" s="38" t="n"/>
       <c r="C219" s="6" t="n"/>
       <c r="K219" s="14" t="n"/>
     </row>
-    <row r="220" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="220" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A220" s="0" t="n"/>
       <c r="B220" s="39" t="n"/>
       <c r="C220" s="7" t="n"/>
       <c r="K220" s="14" t="n"/>
     </row>
-    <row r="221" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="221" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A221" s="0" t="n"/>
       <c r="B221" s="38" t="n"/>
       <c r="C221" s="6" t="n"/>
       <c r="K221" s="14" t="n"/>
     </row>
-    <row r="222" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="222" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A222" s="0" t="n"/>
       <c r="B222" s="38" t="n"/>
       <c r="C222" s="6" t="n"/>
       <c r="K222" s="14" t="n"/>
     </row>
-    <row r="223" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="223" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A223" s="0" t="n"/>
       <c r="B223" s="38" t="n"/>
       <c r="C223" s="6" t="n"/>
       <c r="K223" s="14" t="n"/>
     </row>
-    <row r="224" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="224" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A224" s="0" t="n"/>
       <c r="B224" s="38" t="n"/>
       <c r="C224" s="6" t="n"/>
       <c r="K224" s="14" t="n"/>
     </row>
-    <row r="225" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="225" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A225" s="0" t="n"/>
       <c r="B225" s="38" t="n"/>
       <c r="C225" s="6" t="n"/>
       <c r="K225" s="14" t="n"/>
     </row>
-    <row r="226" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="226" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A226" s="0" t="n"/>
       <c r="B226" s="39" t="n"/>
       <c r="C226" s="7" t="n"/>
       <c r="K226" s="14" t="n"/>
     </row>
-    <row r="227" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="227" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A227" s="0" t="n"/>
       <c r="B227" s="38" t="n"/>
       <c r="C227" s="6" t="n"/>
       <c r="K227" s="14" t="n"/>
     </row>
-    <row r="228" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="228" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A228" s="0" t="n"/>
       <c r="B228" s="38" t="n"/>
       <c r="C228" s="6" t="n"/>
       <c r="K228" s="14" t="n"/>
     </row>
-    <row r="229" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="229" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A229" s="0" t="n"/>
       <c r="B229" s="38" t="n"/>
       <c r="C229" s="6" t="n"/>
       <c r="K229" s="14" t="n"/>
     </row>
-    <row r="230" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="230" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A230" s="0" t="n"/>
       <c r="B230" s="38" t="n"/>
       <c r="C230" s="6" t="n"/>
       <c r="K230" s="14" t="n"/>
     </row>
-    <row r="231" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="231" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A231" s="0" t="n"/>
       <c r="B231" s="38" t="n"/>
       <c r="C231" s="6" t="n"/>
       <c r="K231" s="14" t="n"/>
     </row>
-    <row r="232" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="232" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A232" s="0" t="n"/>
       <c r="B232" s="39" t="n"/>
       <c r="C232" s="7" t="n"/>
       <c r="K232" s="14" t="n"/>
     </row>
-    <row r="233" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="233" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="A233" s="0" t="n"/>
       <c r="B233" s="38" t="n"/>
       <c r="C233" s="6" t="n"/>
       <c r="K233" s="14" t="n"/>
     </row>
-    <row r="234" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="234" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A234" s="0" t="n"/>
       <c r="B234" s="38" t="n"/>
       <c r="C234" s="6" t="n"/>
       <c r="K234" s="14" t="n"/>
     </row>
-    <row r="235" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="235" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A235" s="0" t="n"/>
       <c r="B235" s="38" t="n"/>
       <c r="C235" s="6" t="n"/>
       <c r="K235" s="14" t="n"/>
     </row>
-    <row r="236" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="236" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A236" s="0" t="n"/>
       <c r="B236" s="38" t="n"/>
       <c r="C236" s="6" t="n"/>
       <c r="K236" s="14" t="n"/>
     </row>
-    <row r="237" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="237" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A237" s="0" t="n"/>
       <c r="B237" s="38" t="n"/>
       <c r="C237" s="6" t="n"/>
       <c r="K237" s="14" t="n"/>
     </row>
-    <row r="238" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="238" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="A238" s="0" t="n"/>
       <c r="B238" s="39" t="n"/>
       <c r="C238" s="7" t="n"/>
       <c r="K238" s="14" t="n"/>
     </row>
-    <row r="239" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="239" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B239" s="38" t="n"/>
       <c r="C239" s="6" t="n"/>
       <c r="K239" s="14" t="n"/>
     </row>
-    <row r="240" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="240" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B240" s="38" t="n"/>
       <c r="C240" s="6" t="n"/>
       <c r="K240" s="14" t="n"/>
     </row>
-    <row r="241" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="241" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B241" s="38" t="n"/>
       <c r="C241" s="6" t="n"/>
       <c r="K241" s="14" t="n"/>
     </row>
-    <row r="242" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="242" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B242" s="38" t="n"/>
       <c r="C242" s="6" t="n"/>
       <c r="K242" s="14" t="n"/>
     </row>
-    <row r="243" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="243" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B243" s="38" t="n"/>
       <c r="C243" s="6" t="n"/>
       <c r="K243" s="14" t="n"/>
     </row>
-    <row r="244" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="244" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B244" s="39" t="n"/>
       <c r="C244" s="7" t="n"/>
       <c r="K244" s="14" t="n"/>
     </row>
-    <row r="245" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="245" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B245" s="38" t="n"/>
       <c r="C245" s="6" t="n"/>
       <c r="K245" s="14" t="n"/>
     </row>
-    <row r="246" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="246" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B246" s="38" t="n"/>
       <c r="C246" s="6" t="n"/>
       <c r="K246" s="14" t="n"/>
     </row>
-    <row r="247" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="247" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B247" s="38" t="n"/>
       <c r="C247" s="6" t="n"/>
       <c r="K247" s="14" t="n"/>
     </row>
-    <row r="248" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="248" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B248" s="44" t="n"/>
       <c r="C248" s="15" t="n"/>
       <c r="K248" s="14" t="n"/>
     </row>
-    <row r="249" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="249" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B249" s="38" t="n"/>
       <c r="C249" s="6" t="n"/>
       <c r="K249" s="14" t="n"/>
     </row>
-    <row r="250" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="250" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B250" s="39" t="n"/>
       <c r="C250" s="7" t="n"/>
       <c r="K250" s="14" t="n"/>
     </row>
-    <row r="251" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="251" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B251" s="38" t="n"/>
       <c r="C251" s="6" t="n"/>
       <c r="K251" s="14" t="n"/>
     </row>
-    <row r="252" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="252" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B252" s="38" t="n"/>
       <c r="C252" s="6" t="n"/>
       <c r="K252" s="14" t="n"/>
     </row>
-    <row r="253" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="253" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B253" s="38" t="n"/>
       <c r="C253" s="6" t="n"/>
       <c r="K253" s="14" t="n"/>
     </row>
-    <row r="254" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="254" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B254" s="38" t="n"/>
       <c r="C254" s="6" t="n"/>
       <c r="K254" s="14" t="n"/>
     </row>
-    <row r="255" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="255" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B255" s="38" t="n"/>
       <c r="C255" s="6" t="n"/>
       <c r="K255" s="14" t="n"/>
     </row>
-    <row r="256" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="256" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B256" s="39" t="n"/>
       <c r="C256" s="7" t="n"/>
       <c r="K256" s="14" t="n"/>
     </row>
-    <row r="257" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="257" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B257" s="38" t="n"/>
       <c r="C257" s="6" t="n"/>
       <c r="K257" s="14" t="n"/>
     </row>
-    <row r="258" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="258" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B258" s="38" t="n"/>
       <c r="C258" s="6" t="n"/>
       <c r="K258" s="14" t="n"/>
     </row>
-    <row r="259" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="259" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B259" s="38" t="n"/>
       <c r="C259" s="6" t="n"/>
       <c r="K259" s="14" t="n"/>
     </row>
-    <row r="260" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="260" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B260" s="38" t="n"/>
       <c r="C260" s="6" t="n"/>
       <c r="K260" s="14" t="n"/>
     </row>
-    <row r="261" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="261" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B261" s="38" t="n"/>
       <c r="C261" s="6" t="n"/>
       <c r="K261" s="14" t="n"/>
     </row>
-    <row r="262" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="262" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B262" s="39" t="n"/>
       <c r="C262" s="7" t="n"/>
       <c r="K262" s="14" t="n"/>
     </row>
-    <row r="263" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="263" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B263" s="38" t="n"/>
       <c r="C263" s="6" t="n"/>
       <c r="K263" s="14" t="n"/>
     </row>
-    <row r="264" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="264" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B264" s="38" t="n"/>
       <c r="C264" s="6" t="n"/>
       <c r="K264" s="14" t="n"/>
     </row>
-    <row r="265" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="265" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B265" s="38" t="n"/>
       <c r="C265" s="6" t="n"/>
       <c r="K265" s="14" t="n"/>
     </row>
-    <row r="266" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="266" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B266" s="38" t="n"/>
       <c r="C266" s="6" t="n"/>
       <c r="K266" s="14" t="n"/>
     </row>
-    <row r="267" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="267" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B267" s="38" t="n"/>
       <c r="C267" s="6" t="n"/>
       <c r="K267" s="14" t="n"/>
     </row>
-    <row r="268" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="268" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B268" s="39" t="n"/>
       <c r="C268" s="7" t="n"/>
       <c r="K268" s="14" t="n"/>
     </row>
-    <row r="269" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="269" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B269" s="38" t="n"/>
       <c r="C269" s="6" t="n"/>
     </row>
-    <row r="270" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="270" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B270" s="38" t="n"/>
       <c r="C270" s="6" t="n"/>
     </row>
-    <row r="271" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="271" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B271" s="38" t="n"/>
       <c r="C271" s="6" t="n"/>
     </row>
-    <row r="272" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="272" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B272" s="38" t="n"/>
       <c r="C272" s="6" t="n"/>
     </row>
-    <row r="273" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="273" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B273" s="38" t="n"/>
       <c r="C273" s="6" t="n"/>
     </row>
-    <row r="274" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="274" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B274" s="39" t="n"/>
       <c r="C274" s="7" t="n"/>
     </row>
-    <row r="275" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="275" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B275" s="38" t="n"/>
       <c r="C275" s="6" t="n"/>
     </row>
-    <row r="276" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="276" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B276" s="38" t="n"/>
       <c r="C276" s="6" t="n"/>
     </row>
-    <row r="277" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="277" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B277" s="38" t="n"/>
       <c r="C277" s="6" t="n"/>
     </row>
-    <row r="278" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="278" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B278" s="38" t="n"/>
       <c r="C278" s="6" t="n"/>
     </row>
-    <row r="279" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="279" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B279" s="38" t="n"/>
       <c r="C279" s="6" t="n"/>
     </row>
-    <row r="280" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="280" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B280" s="39" t="n"/>
       <c r="C280" s="7" t="n"/>
     </row>
-    <row r="281" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="281" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B281" s="38" t="n"/>
       <c r="C281" s="6" t="n"/>
     </row>
-    <row r="282" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="282" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B282" s="38" t="n"/>
       <c r="C282" s="6" t="n"/>
     </row>
-    <row r="283" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="283" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B283" s="38" t="n"/>
       <c r="C283" s="6" t="n"/>
     </row>
-    <row r="284" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="284" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B284" s="38" t="n"/>
       <c r="C284" s="6" t="n"/>
     </row>
-    <row r="285" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="285" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B285" s="38" t="n"/>
       <c r="C285" s="6" t="n"/>
     </row>
-    <row r="286" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="286" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B286" s="38" t="n"/>
       <c r="C286" s="6" t="n"/>
     </row>
-    <row r="287" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="287" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B287" s="39" t="n"/>
       <c r="C287" s="7" t="n"/>
     </row>
-    <row r="288" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="288" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B288" s="42" t="n"/>
       <c r="C288" s="43" t="n"/>
     </row>
-    <row r="289" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="289" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B289" s="42" t="n"/>
       <c r="C289" s="43" t="n"/>
     </row>
-    <row r="290" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="290" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B290" s="42" t="n"/>
       <c r="C290" s="43" t="n"/>
     </row>
-    <row r="291" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="291" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B291" s="42" t="n"/>
       <c r="C291" s="43" t="n"/>
     </row>
-    <row r="292" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="292" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B292" s="45" t="n"/>
       <c r="C292" s="46" t="n"/>
     </row>
-    <row r="293" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="293" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B293" s="38" t="n"/>
       <c r="C293" s="6" t="n"/>
     </row>
-    <row r="294" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="294" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B294" s="38" t="n"/>
       <c r="C294" s="6" t="n"/>
     </row>
-    <row r="295" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="295" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B295" s="38" t="n"/>
       <c r="C295" s="6" t="n"/>
     </row>
-    <row r="296" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="296" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B296" s="38" t="n"/>
       <c r="C296" s="6" t="n"/>
     </row>
-    <row r="297" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="297" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B297" s="38" t="n"/>
       <c r="C297" s="6" t="n"/>
     </row>
-    <row r="298" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="298" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B298" s="39" t="n"/>
       <c r="C298" s="7" t="n"/>
     </row>
-    <row r="299" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="299" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B299" s="38" t="n"/>
       <c r="C299" s="6" t="n"/>
     </row>
-    <row r="300" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="300" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B300" s="38" t="n"/>
       <c r="C300" s="6" t="n"/>
     </row>
-    <row r="301" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="301" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B301" s="38" t="n"/>
       <c r="C301" s="6" t="n"/>
     </row>
-    <row r="302" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="302" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B302" s="38" t="n"/>
       <c r="C302" s="6" t="n"/>
     </row>
-    <row r="303" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="303" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B303" s="38" t="n"/>
       <c r="C303" s="6" t="n"/>
     </row>
-    <row r="304" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="304" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B304" s="38" t="n"/>
       <c r="C304" s="6" t="n"/>
     </row>
-    <row r="305" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="305" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B305" s="39" t="n"/>
       <c r="C305" s="7" t="n"/>
     </row>
-    <row r="306" ht="18" customHeight="1" s="80" thickBot="1" thickTop="1">
+    <row r="306" ht="18" customHeight="1" s="73" thickBot="1" thickTop="1">
       <c r="B306" s="38" t="n"/>
       <c r="C306" s="6" t="n"/>
     </row>
-    <row r="307" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="307" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B307" s="38" t="n"/>
       <c r="C307" s="6" t="n"/>
     </row>
-    <row r="308" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="308" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B308" s="38" t="n"/>
       <c r="C308" s="6" t="n"/>
     </row>
-    <row r="309" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="309" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B309" s="38" t="n"/>
       <c r="C309" s="6" t="n"/>
     </row>
-    <row r="310" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="310" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B310" s="38" t="n"/>
       <c r="C310" s="6" t="n"/>
     </row>
-    <row r="311" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="311" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B311" s="38" t="n"/>
       <c r="C311" s="6" t="n"/>
     </row>
-    <row r="312" ht="17.25" customHeight="1" s="80" thickBot="1">
+    <row r="312" ht="17.25" customHeight="1" s="73" thickBot="1">
       <c r="B312" s="39" t="n"/>
       <c r="C312" s="7" t="n"/>
     </row>
-    <row r="313" ht="17.25" customHeight="1" s="80" thickTop="1"/>
+    <row r="313" ht="17.25" customHeight="1" s="73" thickTop="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId1"/>
@@ -7803,51 +7698,51 @@
   <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="80" thickBot="1">
-      <c r="A1" s="81" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="73" thickBot="1">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>분반정보</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="83" t="n"/>
-      <c r="D1" s="84" t="inlineStr">
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="68" t="inlineStr">
         <is>
           <t>학생정보</t>
         </is>
       </c>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
-      <c r="G1" s="82" t="n"/>
-      <c r="H1" s="82" t="n"/>
-      <c r="I1" s="82" t="n"/>
-      <c r="J1" s="83" t="n"/>
-      <c r="K1" s="85" t="inlineStr">
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="67" t="n"/>
+      <c r="K1" s="66" t="inlineStr">
         <is>
           <t>학부모정보</t>
         </is>
       </c>
-      <c r="L1" s="83" t="n"/>
-      <c r="M1" s="86" t="inlineStr">
+      <c r="L1" s="67" t="n"/>
+      <c r="M1" s="71" t="inlineStr">
         <is>
           <t>출석부</t>
         </is>
       </c>
-      <c r="N1" s="82" t="n"/>
-      <c r="O1" s="82" t="n"/>
-      <c r="P1" s="82" t="n"/>
-      <c r="Q1" s="82" t="n"/>
-      <c r="R1" s="82" t="n"/>
-      <c r="S1" s="82" t="n"/>
-      <c r="T1" s="82" t="n"/>
-      <c r="U1" s="83" t="n"/>
-      <c r="V1" s="87" t="inlineStr">
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="67" t="n"/>
+      <c r="V1" s="64" t="inlineStr">
         <is>
           <t>USB포트유무</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="80" thickBot="1">
+    <row r="2" ht="33.75" customHeight="1" s="73" thickBot="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
           <t>분반</t>
@@ -7953,18 +7848,18 @@
           <t>이슈사항</t>
         </is>
       </c>
-      <c r="V2" s="88" t="n"/>
-    </row>
-    <row r="3" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A3" s="89" t="n">
+      <c r="V2" s="65" t="n"/>
+    </row>
+    <row r="3" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A3" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="90" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>이정은</t>
         </is>
       </c>
-      <c r="C3" s="90" t="n">
+      <c r="C3" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D3" s="20" t="inlineStr">
@@ -8021,10 +7916,10 @@
       <c r="U3" s="23" t="n"/>
       <c r="V3" s="24" t="n"/>
     </row>
-    <row r="4" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A4" s="91" t="n"/>
-      <c r="B4" s="92" t="n"/>
-      <c r="C4" s="92" t="n"/>
+    <row r="4" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A4" s="59" t="n"/>
+      <c r="B4" s="62" t="n"/>
+      <c r="C4" s="62" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -8079,10 +7974,10 @@
       <c r="U4" s="23" t="n"/>
       <c r="V4" s="24" t="n"/>
     </row>
-    <row r="5" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A5" s="91" t="n"/>
-      <c r="B5" s="92" t="n"/>
-      <c r="C5" s="92" t="n"/>
+    <row r="5" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A5" s="59" t="n"/>
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -8137,10 +8032,10 @@
       <c r="U5" s="23" t="n"/>
       <c r="V5" s="24" t="n"/>
     </row>
-    <row r="6" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A6" s="91" t="n"/>
-      <c r="B6" s="92" t="n"/>
-      <c r="C6" s="92" t="n"/>
+    <row r="6" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A6" s="59" t="n"/>
+      <c r="B6" s="62" t="n"/>
+      <c r="C6" s="62" t="n"/>
       <c r="D6" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8195,10 +8090,10 @@
       <c r="U6" s="23" t="n"/>
       <c r="V6" s="24" t="n"/>
     </row>
-    <row r="7" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A7" s="91" t="n"/>
-      <c r="B7" s="92" t="n"/>
-      <c r="C7" s="92" t="n"/>
+    <row r="7" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A7" s="59" t="n"/>
+      <c r="B7" s="62" t="n"/>
+      <c r="C7" s="62" t="n"/>
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -8253,10 +8148,10 @@
       <c r="U7" s="23" t="n"/>
       <c r="V7" s="24" t="n"/>
     </row>
-    <row r="8" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A8" s="93" t="n"/>
-      <c r="B8" s="94" t="n"/>
-      <c r="C8" s="94" t="n"/>
+    <row r="8" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A8" s="60" t="n"/>
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="63" t="n"/>
       <c r="D8" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8311,16 +8206,16 @@
       <c r="U8" s="28" t="n"/>
       <c r="V8" s="29" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A9" s="89" t="n">
+    <row r="9" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A9" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="90" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>황선희</t>
         </is>
       </c>
-      <c r="C9" s="90" t="n">
+      <c r="C9" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8377,10 +8272,10 @@
       <c r="U9" s="23" t="n"/>
       <c r="V9" s="24" t="n"/>
     </row>
-    <row r="10" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A10" s="91" t="n"/>
-      <c r="B10" s="92" t="n"/>
-      <c r="C10" s="92" t="n"/>
+    <row r="10" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A10" s="59" t="n"/>
+      <c r="B10" s="62" t="n"/>
+      <c r="C10" s="62" t="n"/>
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -8435,10 +8330,10 @@
       <c r="U10" s="23" t="n"/>
       <c r="V10" s="24" t="n"/>
     </row>
-    <row r="11" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A11" s="91" t="n"/>
-      <c r="B11" s="92" t="n"/>
-      <c r="C11" s="92" t="n"/>
+    <row r="11" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A11" s="59" t="n"/>
+      <c r="B11" s="62" t="n"/>
+      <c r="C11" s="62" t="n"/>
       <c r="D11" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8493,10 +8388,10 @@
       <c r="U11" s="23" t="n"/>
       <c r="V11" s="24" t="n"/>
     </row>
-    <row r="12" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A12" s="91" t="n"/>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
+    <row r="12" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A12" s="59" t="n"/>
+      <c r="B12" s="62" t="n"/>
+      <c r="C12" s="62" t="n"/>
       <c r="D12" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8551,10 +8446,10 @@
       <c r="U12" s="23" t="n"/>
       <c r="V12" s="24" t="n"/>
     </row>
-    <row r="13" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A13" s="91" t="n"/>
-      <c r="B13" s="92" t="n"/>
-      <c r="C13" s="92" t="n"/>
+    <row r="13" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A13" s="59" t="n"/>
+      <c r="B13" s="62" t="n"/>
+      <c r="C13" s="62" t="n"/>
       <c r="D13" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8609,10 +8504,10 @@
       <c r="U13" s="23" t="n"/>
       <c r="V13" s="24" t="n"/>
     </row>
-    <row r="14" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A14" s="93" t="n"/>
-      <c r="B14" s="94" t="n"/>
-      <c r="C14" s="94" t="n"/>
+    <row r="14" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A14" s="60" t="n"/>
+      <c r="B14" s="63" t="n"/>
+      <c r="C14" s="63" t="n"/>
       <c r="D14" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -8667,16 +8562,16 @@
       <c r="U14" s="28" t="n"/>
       <c r="V14" s="29" t="n"/>
     </row>
-    <row r="15" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A15" s="89" t="n">
+    <row r="15" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A15" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="90" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>김화경</t>
         </is>
       </c>
-      <c r="C15" s="90" t="n">
+      <c r="C15" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8733,10 +8628,10 @@
       <c r="U15" s="23" t="n"/>
       <c r="V15" s="24" t="n"/>
     </row>
-    <row r="16" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A16" s="91" t="n"/>
-      <c r="B16" s="92" t="n"/>
-      <c r="C16" s="92" t="n"/>
+    <row r="16" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A16" s="59" t="n"/>
+      <c r="B16" s="62" t="n"/>
+      <c r="C16" s="62" t="n"/>
       <c r="D16" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -8791,10 +8686,10 @@
       <c r="U16" s="23" t="n"/>
       <c r="V16" s="24" t="n"/>
     </row>
-    <row r="17" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A17" s="91" t="n"/>
-      <c r="B17" s="92" t="n"/>
-      <c r="C17" s="92" t="n"/>
+    <row r="17" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A17" s="59" t="n"/>
+      <c r="B17" s="62" t="n"/>
+      <c r="C17" s="62" t="n"/>
       <c r="D17" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8849,10 +8744,10 @@
       <c r="U17" s="23" t="n"/>
       <c r="V17" s="24" t="n"/>
     </row>
-    <row r="18" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A18" s="91" t="n"/>
-      <c r="B18" s="92" t="n"/>
-      <c r="C18" s="92" t="n"/>
+    <row r="18" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A18" s="59" t="n"/>
+      <c r="B18" s="62" t="n"/>
+      <c r="C18" s="62" t="n"/>
       <c r="D18" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8907,10 +8802,10 @@
       <c r="U18" s="23" t="n"/>
       <c r="V18" s="24" t="n"/>
     </row>
-    <row r="19" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A19" s="91" t="n"/>
-      <c r="B19" s="92" t="n"/>
-      <c r="C19" s="92" t="n"/>
+    <row r="19" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A19" s="59" t="n"/>
+      <c r="B19" s="62" t="n"/>
+      <c r="C19" s="62" t="n"/>
       <c r="D19" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -8965,10 +8860,10 @@
       <c r="U19" s="23" t="n"/>
       <c r="V19" s="24" t="n"/>
     </row>
-    <row r="20" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A20" s="93" t="n"/>
-      <c r="B20" s="94" t="n"/>
-      <c r="C20" s="94" t="n"/>
+    <row r="20" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A20" s="60" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="63" t="n"/>
       <c r="D20" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -9023,16 +8918,16 @@
       <c r="U20" s="28" t="n"/>
       <c r="V20" s="29" t="n"/>
     </row>
-    <row r="21" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A21" s="89" t="n">
+    <row r="21" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A21" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>이양득</t>
         </is>
       </c>
-      <c r="C21" s="90" t="n">
+      <c r="C21" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -9089,10 +8984,10 @@
       <c r="U21" s="23" t="n"/>
       <c r="V21" s="24" t="n"/>
     </row>
-    <row r="22" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A22" s="91" t="n"/>
-      <c r="B22" s="92" t="n"/>
-      <c r="C22" s="92" t="n"/>
+    <row r="22" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A22" s="59" t="n"/>
+      <c r="B22" s="62" t="n"/>
+      <c r="C22" s="62" t="n"/>
       <c r="D22" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9147,10 +9042,10 @@
       <c r="U22" s="23" t="n"/>
       <c r="V22" s="24" t="n"/>
     </row>
-    <row r="23" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A23" s="91" t="n"/>
-      <c r="B23" s="92" t="n"/>
-      <c r="C23" s="92" t="n"/>
+    <row r="23" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A23" s="59" t="n"/>
+      <c r="B23" s="62" t="n"/>
+      <c r="C23" s="62" t="n"/>
       <c r="D23" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9205,10 +9100,10 @@
       <c r="U23" s="23" t="n"/>
       <c r="V23" s="24" t="n"/>
     </row>
-    <row r="24" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A24" s="91" t="n"/>
-      <c r="B24" s="92" t="n"/>
-      <c r="C24" s="92" t="n"/>
+    <row r="24" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A24" s="59" t="n"/>
+      <c r="B24" s="62" t="n"/>
+      <c r="C24" s="62" t="n"/>
       <c r="D24" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -9263,10 +9158,10 @@
       <c r="U24" s="23" t="n"/>
       <c r="V24" s="24" t="n"/>
     </row>
-    <row r="25" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A25" s="91" t="n"/>
-      <c r="B25" s="92" t="n"/>
-      <c r="C25" s="92" t="n"/>
+    <row r="25" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A25" s="59" t="n"/>
+      <c r="B25" s="62" t="n"/>
+      <c r="C25" s="62" t="n"/>
       <c r="D25" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9321,10 +9216,10 @@
       <c r="U25" s="23" t="n"/>
       <c r="V25" s="24" t="n"/>
     </row>
-    <row r="26" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A26" s="93" t="n"/>
-      <c r="B26" s="94" t="n"/>
-      <c r="C26" s="94" t="n"/>
+    <row r="26" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A26" s="60" t="n"/>
+      <c r="B26" s="63" t="n"/>
+      <c r="C26" s="63" t="n"/>
       <c r="D26" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -9379,16 +9274,16 @@
       <c r="U26" s="28" t="n"/>
       <c r="V26" s="29" t="n"/>
     </row>
-    <row r="27" ht="34.5" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A27" s="89" t="n">
+    <row r="27" ht="34.5" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A27" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="90" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>이예봉</t>
         </is>
       </c>
-      <c r="C27" s="90" t="n">
+      <c r="C27" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -9445,10 +9340,10 @@
       <c r="U27" s="23" t="n"/>
       <c r="V27" s="24" t="n"/>
     </row>
-    <row r="28" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A28" s="91" t="n"/>
-      <c r="B28" s="92" t="n"/>
-      <c r="C28" s="92" t="n"/>
+    <row r="28" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A28" s="59" t="n"/>
+      <c r="B28" s="62" t="n"/>
+      <c r="C28" s="62" t="n"/>
       <c r="D28" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -9503,10 +9398,10 @@
       <c r="U28" s="23" t="n"/>
       <c r="V28" s="24" t="n"/>
     </row>
-    <row r="29" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A29" s="91" t="n"/>
-      <c r="B29" s="92" t="n"/>
-      <c r="C29" s="92" t="n"/>
+    <row r="29" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A29" s="59" t="n"/>
+      <c r="B29" s="62" t="n"/>
+      <c r="C29" s="62" t="n"/>
       <c r="D29" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9561,10 +9456,10 @@
       <c r="U29" s="23" t="n"/>
       <c r="V29" s="24" t="n"/>
     </row>
-    <row r="30" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A30" s="91" t="n"/>
-      <c r="B30" s="92" t="n"/>
-      <c r="C30" s="92" t="n"/>
+    <row r="30" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A30" s="59" t="n"/>
+      <c r="B30" s="62" t="n"/>
+      <c r="C30" s="62" t="n"/>
       <c r="D30" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -9619,10 +9514,10 @@
       <c r="U30" s="23" t="n"/>
       <c r="V30" s="24" t="n"/>
     </row>
-    <row r="31" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A31" s="91" t="n"/>
-      <c r="B31" s="92" t="n"/>
-      <c r="C31" s="92" t="n"/>
+    <row r="31" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A31" s="59" t="n"/>
+      <c r="B31" s="62" t="n"/>
+      <c r="C31" s="62" t="n"/>
       <c r="D31" s="20" t="inlineStr">
         <is>
           <t>6 회</t>
@@ -9677,10 +9572,10 @@
       <c r="U31" s="23" t="n"/>
       <c r="V31" s="24" t="n"/>
     </row>
-    <row r="32" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A32" s="93" t="n"/>
-      <c r="B32" s="94" t="n"/>
-      <c r="C32" s="94" t="n"/>
+    <row r="32" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A32" s="60" t="n"/>
+      <c r="B32" s="63" t="n"/>
+      <c r="C32" s="63" t="n"/>
       <c r="D32" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9735,16 +9630,16 @@
       <c r="U32" s="28" t="n"/>
       <c r="V32" s="29" t="n"/>
     </row>
-    <row r="33" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A33" s="89" t="n">
+    <row r="33" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A33" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="90" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>김경진</t>
         </is>
       </c>
-      <c r="C33" s="90" t="n">
+      <c r="C33" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -9801,10 +9696,10 @@
       <c r="U33" s="23" t="n"/>
       <c r="V33" s="24" t="n"/>
     </row>
-    <row r="34" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A34" s="91" t="n"/>
-      <c r="B34" s="92" t="n"/>
-      <c r="C34" s="92" t="n"/>
+    <row r="34" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A34" s="59" t="n"/>
+      <c r="B34" s="62" t="n"/>
+      <c r="C34" s="62" t="n"/>
       <c r="D34" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -9859,10 +9754,10 @@
       <c r="U34" s="23" t="n"/>
       <c r="V34" s="24" t="n"/>
     </row>
-    <row r="35" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A35" s="91" t="n"/>
-      <c r="B35" s="92" t="n"/>
-      <c r="C35" s="92" t="n"/>
+    <row r="35" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A35" s="59" t="n"/>
+      <c r="B35" s="62" t="n"/>
+      <c r="C35" s="62" t="n"/>
       <c r="D35" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -9917,10 +9812,10 @@
       <c r="U35" s="23" t="n"/>
       <c r="V35" s="24" t="n"/>
     </row>
-    <row r="36" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A36" s="91" t="n"/>
-      <c r="B36" s="92" t="n"/>
-      <c r="C36" s="92" t="n"/>
+    <row r="36" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A36" s="59" t="n"/>
+      <c r="B36" s="62" t="n"/>
+      <c r="C36" s="62" t="n"/>
       <c r="D36" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -9975,10 +9870,10 @@
       <c r="U36" s="23" t="n"/>
       <c r="V36" s="24" t="n"/>
     </row>
-    <row r="37" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A37" s="91" t="n"/>
-      <c r="B37" s="92" t="n"/>
-      <c r="C37" s="92" t="n"/>
+    <row r="37" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A37" s="59" t="n"/>
+      <c r="B37" s="62" t="n"/>
+      <c r="C37" s="62" t="n"/>
       <c r="D37" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10033,10 +9928,10 @@
       <c r="U37" s="23" t="n"/>
       <c r="V37" s="24" t="n"/>
     </row>
-    <row r="38" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A38" s="93" t="n"/>
-      <c r="B38" s="94" t="n"/>
-      <c r="C38" s="94" t="n"/>
+    <row r="38" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A38" s="60" t="n"/>
+      <c r="B38" s="63" t="n"/>
+      <c r="C38" s="63" t="n"/>
       <c r="D38" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -10091,16 +9986,16 @@
       <c r="U38" s="28" t="n"/>
       <c r="V38" s="29" t="n"/>
     </row>
-    <row r="39" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A39" s="89" t="n">
+    <row r="39" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A39" s="58" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="90" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>이주원</t>
         </is>
       </c>
-      <c r="C39" s="90" t="n">
+      <c r="C39" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -10157,10 +10052,10 @@
       <c r="U39" s="23" t="n"/>
       <c r="V39" s="24" t="n"/>
     </row>
-    <row r="40" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A40" s="91" t="n"/>
-      <c r="B40" s="92" t="n"/>
-      <c r="C40" s="92" t="n"/>
+    <row r="40" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A40" s="59" t="n"/>
+      <c r="B40" s="62" t="n"/>
+      <c r="C40" s="62" t="n"/>
       <c r="D40" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10215,10 +10110,10 @@
       <c r="U40" s="23" t="n"/>
       <c r="V40" s="24" t="n"/>
     </row>
-    <row r="41" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A41" s="91" t="n"/>
-      <c r="B41" s="92" t="n"/>
-      <c r="C41" s="92" t="n"/>
+    <row r="41" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A41" s="59" t="n"/>
+      <c r="B41" s="62" t="n"/>
+      <c r="C41" s="62" t="n"/>
       <c r="D41" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -10273,10 +10168,10 @@
       <c r="U41" s="23" t="n"/>
       <c r="V41" s="24" t="n"/>
     </row>
-    <row r="42" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A42" s="91" t="n"/>
-      <c r="B42" s="92" t="n"/>
-      <c r="C42" s="92" t="n"/>
+    <row r="42" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A42" s="59" t="n"/>
+      <c r="B42" s="62" t="n"/>
+      <c r="C42" s="62" t="n"/>
       <c r="D42" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -10331,10 +10226,10 @@
       <c r="U42" s="23" t="n"/>
       <c r="V42" s="24" t="n"/>
     </row>
-    <row r="43" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A43" s="91" t="n"/>
-      <c r="B43" s="92" t="n"/>
-      <c r="C43" s="92" t="n"/>
+    <row r="43" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A43" s="59" t="n"/>
+      <c r="B43" s="62" t="n"/>
+      <c r="C43" s="62" t="n"/>
       <c r="D43" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10389,10 +10284,10 @@
       <c r="U43" s="23" t="n"/>
       <c r="V43" s="24" t="n"/>
     </row>
-    <row r="44" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A44" s="93" t="n"/>
-      <c r="B44" s="94" t="n"/>
-      <c r="C44" s="94" t="n"/>
+    <row r="44" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A44" s="60" t="n"/>
+      <c r="B44" s="63" t="n"/>
+      <c r="C44" s="63" t="n"/>
       <c r="D44" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -10447,16 +10342,16 @@
       <c r="U44" s="28" t="n"/>
       <c r="V44" s="29" t="n"/>
     </row>
-    <row r="45" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A45" s="89" t="n">
+    <row r="45" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A45" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="B45" s="90" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>장은영</t>
         </is>
       </c>
-      <c r="C45" s="90" t="n">
+      <c r="C45" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -10513,10 +10408,10 @@
       <c r="U45" s="23" t="n"/>
       <c r="V45" s="24" t="n"/>
     </row>
-    <row r="46" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A46" s="91" t="n"/>
-      <c r="B46" s="92" t="n"/>
-      <c r="C46" s="92" t="n"/>
+    <row r="46" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A46" s="59" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
       <c r="D46" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -10571,10 +10466,10 @@
       <c r="U46" s="23" t="n"/>
       <c r="V46" s="24" t="n"/>
     </row>
-    <row r="47" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A47" s="91" t="n"/>
-      <c r="B47" s="92" t="n"/>
-      <c r="C47" s="92" t="n"/>
+    <row r="47" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
       <c r="D47" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -10629,10 +10524,10 @@
       <c r="U47" s="23" t="n"/>
       <c r="V47" s="24" t="n"/>
     </row>
-    <row r="48" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A48" s="91" t="n"/>
-      <c r="B48" s="92" t="n"/>
-      <c r="C48" s="92" t="n"/>
+    <row r="48" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
       <c r="D48" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10687,10 +10582,10 @@
       <c r="U48" s="23" t="n"/>
       <c r="V48" s="24" t="n"/>
     </row>
-    <row r="49" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A49" s="93" t="n"/>
-      <c r="B49" s="94" t="n"/>
-      <c r="C49" s="94" t="n"/>
+    <row r="49" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A49" s="60" t="n"/>
+      <c r="B49" s="63" t="n"/>
+      <c r="C49" s="63" t="n"/>
       <c r="D49" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -10745,16 +10640,16 @@
       <c r="U49" s="28" t="n"/>
       <c r="V49" s="29" t="n"/>
     </row>
-    <row r="50" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A50" s="89" t="n">
+    <row r="50" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A50" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="B50" s="90" t="inlineStr">
+      <c r="B50" s="61" t="inlineStr">
         <is>
           <t>황수리</t>
         </is>
       </c>
-      <c r="C50" s="90" t="n">
+      <c r="C50" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D50" s="20" t="inlineStr">
@@ -10811,10 +10706,10 @@
       <c r="U50" s="23" t="n"/>
       <c r="V50" s="24" t="n"/>
     </row>
-    <row r="51" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A51" s="91" t="n"/>
-      <c r="B51" s="92" t="n"/>
-      <c r="C51" s="92" t="n"/>
+    <row r="51" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A51" s="59" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
       <c r="D51" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -10869,10 +10764,10 @@
       <c r="U51" s="23" t="n"/>
       <c r="V51" s="24" t="n"/>
     </row>
-    <row r="52" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A52" s="91" t="n"/>
-      <c r="B52" s="92" t="n"/>
-      <c r="C52" s="92" t="n"/>
+    <row r="52" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A52" s="59" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
       <c r="D52" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10927,10 +10822,10 @@
       <c r="U52" s="23" t="n"/>
       <c r="V52" s="24" t="n"/>
     </row>
-    <row r="53" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A53" s="91" t="n"/>
-      <c r="B53" s="92" t="n"/>
-      <c r="C53" s="92" t="n"/>
+    <row r="53" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A53" s="59" t="n"/>
+      <c r="B53" s="62" t="n"/>
+      <c r="C53" s="62" t="n"/>
       <c r="D53" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -10985,10 +10880,10 @@
       <c r="U53" s="23" t="n"/>
       <c r="V53" s="24" t="n"/>
     </row>
-    <row r="54" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A54" s="93" t="n"/>
-      <c r="B54" s="94" t="n"/>
-      <c r="C54" s="94" t="n"/>
+    <row r="54" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A54" s="60" t="n"/>
+      <c r="B54" s="63" t="n"/>
+      <c r="C54" s="63" t="n"/>
       <c r="D54" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -11043,16 +10938,16 @@
       <c r="U54" s="28" t="n"/>
       <c r="V54" s="29" t="n"/>
     </row>
-    <row r="55" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A55" s="89" t="n">
+    <row r="55" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A55" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="90" t="inlineStr">
+      <c r="B55" s="61" t="inlineStr">
         <is>
           <t>김현지</t>
         </is>
       </c>
-      <c r="C55" s="90" t="n">
+      <c r="C55" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -11109,10 +11004,10 @@
       <c r="U55" s="23" t="n"/>
       <c r="V55" s="24" t="n"/>
     </row>
-    <row r="56" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A56" s="91" t="n"/>
-      <c r="B56" s="92" t="n"/>
-      <c r="C56" s="92" t="n"/>
+    <row r="56" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A56" s="59" t="n"/>
+      <c r="B56" s="62" t="n"/>
+      <c r="C56" s="62" t="n"/>
       <c r="D56" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -11167,10 +11062,10 @@
       <c r="U56" s="23" t="n"/>
       <c r="V56" s="24" t="n"/>
     </row>
-    <row r="57" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A57" s="91" t="n"/>
-      <c r="B57" s="92" t="n"/>
-      <c r="C57" s="92" t="n"/>
+    <row r="57" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A57" s="59" t="n"/>
+      <c r="B57" s="62" t="n"/>
+      <c r="C57" s="62" t="n"/>
       <c r="D57" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11225,10 +11120,10 @@
       <c r="U57" s="23" t="n"/>
       <c r="V57" s="24" t="n"/>
     </row>
-    <row r="58" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A58" s="91" t="n"/>
-      <c r="B58" s="92" t="n"/>
-      <c r="C58" s="92" t="n"/>
+    <row r="58" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A58" s="59" t="n"/>
+      <c r="B58" s="62" t="n"/>
+      <c r="C58" s="62" t="n"/>
       <c r="D58" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11283,10 +11178,10 @@
       <c r="U58" s="23" t="n"/>
       <c r="V58" s="24" t="n"/>
     </row>
-    <row r="59" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A59" s="91" t="n"/>
-      <c r="B59" s="92" t="n"/>
-      <c r="C59" s="92" t="n"/>
+    <row r="59" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="62" t="n"/>
+      <c r="C59" s="62" t="n"/>
       <c r="D59" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -11337,10 +11232,10 @@
       <c r="U59" s="23" t="n"/>
       <c r="V59" s="24" t="n"/>
     </row>
-    <row r="60" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A60" s="93" t="n"/>
-      <c r="B60" s="94" t="n"/>
-      <c r="C60" s="94" t="n"/>
+    <row r="60" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A60" s="60" t="n"/>
+      <c r="B60" s="63" t="n"/>
+      <c r="C60" s="63" t="n"/>
       <c r="D60" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -11395,16 +11290,16 @@
       <c r="U60" s="28" t="n"/>
       <c r="V60" s="29" t="n"/>
     </row>
-    <row r="61" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A61" s="89" t="n">
+    <row r="61" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A61" s="58" t="n">
         <v>11</v>
       </c>
-      <c r="B61" s="90" t="inlineStr">
+      <c r="B61" s="61" t="inlineStr">
         <is>
           <t>안소영</t>
         </is>
       </c>
-      <c r="C61" s="90" t="n">
+      <c r="C61" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -11461,10 +11356,10 @@
       <c r="U61" s="23" t="n"/>
       <c r="V61" s="30" t="n"/>
     </row>
-    <row r="62" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A62" s="91" t="n"/>
-      <c r="B62" s="92" t="n"/>
-      <c r="C62" s="92" t="n"/>
+    <row r="62" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A62" s="59" t="n"/>
+      <c r="B62" s="62" t="n"/>
+      <c r="C62" s="62" t="n"/>
       <c r="D62" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -11519,10 +11414,10 @@
       <c r="U62" s="23" t="n"/>
       <c r="V62" s="30" t="n"/>
     </row>
-    <row r="63" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A63" s="91" t="n"/>
-      <c r="B63" s="92" t="n"/>
-      <c r="C63" s="92" t="n"/>
+    <row r="63" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A63" s="59" t="n"/>
+      <c r="B63" s="62" t="n"/>
+      <c r="C63" s="62" t="n"/>
       <c r="D63" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -11577,10 +11472,10 @@
       <c r="U63" s="23" t="n"/>
       <c r="V63" s="30" t="n"/>
     </row>
-    <row r="64" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A64" s="91" t="n"/>
-      <c r="B64" s="92" t="n"/>
-      <c r="C64" s="92" t="n"/>
+    <row r="64" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A64" s="59" t="n"/>
+      <c r="B64" s="62" t="n"/>
+      <c r="C64" s="62" t="n"/>
       <c r="D64" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -11635,10 +11530,10 @@
       <c r="U64" s="23" t="n"/>
       <c r="V64" s="30" t="n"/>
     </row>
-    <row r="65" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A65" s="91" t="n"/>
-      <c r="B65" s="92" t="n"/>
-      <c r="C65" s="92" t="n"/>
+    <row r="65" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A65" s="59" t="n"/>
+      <c r="B65" s="62" t="n"/>
+      <c r="C65" s="62" t="n"/>
       <c r="D65" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11693,10 +11588,10 @@
       <c r="U65" s="23" t="n"/>
       <c r="V65" s="22" t="n"/>
     </row>
-    <row r="66" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A66" s="93" t="n"/>
-      <c r="B66" s="94" t="n"/>
-      <c r="C66" s="94" t="n"/>
+    <row r="66" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A66" s="60" t="n"/>
+      <c r="B66" s="63" t="n"/>
+      <c r="C66" s="63" t="n"/>
       <c r="D66" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11751,16 +11646,16 @@
       <c r="U66" s="28" t="n"/>
       <c r="V66" s="31" t="n"/>
     </row>
-    <row r="67" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A67" s="89" t="n">
+    <row r="67" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A67" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="B67" s="90" t="inlineStr">
+      <c r="B67" s="61" t="inlineStr">
         <is>
           <t>김숙희</t>
         </is>
       </c>
-      <c r="C67" s="90" t="n">
+      <c r="C67" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -11817,10 +11712,10 @@
       <c r="U67" s="23" t="n"/>
       <c r="V67" s="30" t="n"/>
     </row>
-    <row r="68" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A68" s="91" t="n"/>
-      <c r="B68" s="92" t="n"/>
-      <c r="C68" s="92" t="n"/>
+    <row r="68" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A68" s="59" t="n"/>
+      <c r="B68" s="62" t="n"/>
+      <c r="C68" s="62" t="n"/>
       <c r="D68" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11875,10 +11770,10 @@
       <c r="U68" s="23" t="n"/>
       <c r="V68" s="30" t="n"/>
     </row>
-    <row r="69" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A69" s="91" t="n"/>
-      <c r="B69" s="92" t="n"/>
-      <c r="C69" s="92" t="n"/>
+    <row r="69" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A69" s="59" t="n"/>
+      <c r="B69" s="62" t="n"/>
+      <c r="C69" s="62" t="n"/>
       <c r="D69" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11933,10 +11828,10 @@
       <c r="U69" s="23" t="n"/>
       <c r="V69" s="30" t="n"/>
     </row>
-    <row r="70" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A70" s="91" t="n"/>
-      <c r="B70" s="92" t="n"/>
-      <c r="C70" s="92" t="n"/>
+    <row r="70" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A70" s="59" t="n"/>
+      <c r="B70" s="62" t="n"/>
+      <c r="C70" s="62" t="n"/>
       <c r="D70" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -11991,10 +11886,10 @@
       <c r="U70" s="23" t="n"/>
       <c r="V70" s="30" t="n"/>
     </row>
-    <row r="71" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A71" s="91" t="n"/>
-      <c r="B71" s="92" t="n"/>
-      <c r="C71" s="92" t="n"/>
+    <row r="71" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A71" s="59" t="n"/>
+      <c r="B71" s="62" t="n"/>
+      <c r="C71" s="62" t="n"/>
       <c r="D71" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -12049,10 +11944,10 @@
       <c r="U71" s="23" t="n"/>
       <c r="V71" s="30" t="n"/>
     </row>
-    <row r="72" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A72" s="93" t="n"/>
-      <c r="B72" s="94" t="n"/>
-      <c r="C72" s="94" t="n"/>
+    <row r="72" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A72" s="60" t="n"/>
+      <c r="B72" s="63" t="n"/>
+      <c r="C72" s="63" t="n"/>
       <c r="D72" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12107,16 +12002,16 @@
       <c r="U72" s="28" t="n"/>
       <c r="V72" s="31" t="n"/>
     </row>
-    <row r="73" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A73" s="89" t="n">
+    <row r="73" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A73" s="58" t="n">
         <v>13</v>
       </c>
-      <c r="B73" s="90" t="inlineStr">
+      <c r="B73" s="61" t="inlineStr">
         <is>
           <t>박지윤</t>
         </is>
       </c>
-      <c r="C73" s="90" t="n">
+      <c r="C73" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -12173,10 +12068,10 @@
       <c r="U73" s="23" t="n"/>
       <c r="V73" s="30" t="n"/>
     </row>
-    <row r="74" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A74" s="91" t="n"/>
-      <c r="B74" s="92" t="n"/>
-      <c r="C74" s="92" t="n"/>
+    <row r="74" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A74" s="59" t="n"/>
+      <c r="B74" s="62" t="n"/>
+      <c r="C74" s="62" t="n"/>
       <c r="D74" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12231,10 +12126,10 @@
       <c r="U74" s="23" t="n"/>
       <c r="V74" s="30" t="n"/>
     </row>
-    <row r="75" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A75" s="91" t="n"/>
-      <c r="B75" s="92" t="n"/>
-      <c r="C75" s="92" t="n"/>
+    <row r="75" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A75" s="59" t="n"/>
+      <c r="B75" s="62" t="n"/>
+      <c r="C75" s="62" t="n"/>
       <c r="D75" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -12289,10 +12184,10 @@
       <c r="U75" s="23" t="n"/>
       <c r="V75" s="30" t="n"/>
     </row>
-    <row r="76" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A76" s="91" t="n"/>
-      <c r="B76" s="92" t="n"/>
-      <c r="C76" s="92" t="n"/>
+    <row r="76" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A76" s="59" t="n"/>
+      <c r="B76" s="62" t="n"/>
+      <c r="C76" s="62" t="n"/>
       <c r="D76" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12347,10 +12242,10 @@
       <c r="U76" s="23" t="n"/>
       <c r="V76" s="30" t="n"/>
     </row>
-    <row r="77" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A77" s="93" t="n"/>
-      <c r="B77" s="94" t="n"/>
-      <c r="C77" s="94" t="n"/>
+    <row r="77" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A77" s="60" t="n"/>
+      <c r="B77" s="63" t="n"/>
+      <c r="C77" s="63" t="n"/>
       <c r="D77" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12405,16 +12300,16 @@
       <c r="U77" s="28" t="n"/>
       <c r="V77" s="31" t="n"/>
     </row>
-    <row r="78" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A78" s="89" t="n">
+    <row r="78" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A78" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="B78" s="90" t="inlineStr">
+      <c r="B78" s="61" t="inlineStr">
         <is>
           <t>정성욱</t>
         </is>
       </c>
-      <c r="C78" s="90" t="n">
+      <c r="C78" s="61" t="n">
         <v>7</v>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -12471,10 +12366,10 @@
       <c r="U78" s="23" t="n"/>
       <c r="V78" s="30" t="n"/>
     </row>
-    <row r="79" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A79" s="91" t="n"/>
-      <c r="B79" s="92" t="n"/>
-      <c r="C79" s="92" t="n"/>
+    <row r="79" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A79" s="59" t="n"/>
+      <c r="B79" s="62" t="n"/>
+      <c r="C79" s="62" t="n"/>
       <c r="D79" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -12529,10 +12424,10 @@
       <c r="U79" s="23" t="n"/>
       <c r="V79" s="30" t="n"/>
     </row>
-    <row r="80" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A80" s="91" t="n"/>
-      <c r="B80" s="92" t="n"/>
-      <c r="C80" s="92" t="n"/>
+    <row r="80" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A80" s="59" t="n"/>
+      <c r="B80" s="62" t="n"/>
+      <c r="C80" s="62" t="n"/>
       <c r="D80" s="36" t="inlineStr">
         <is>
           <t>7 회</t>
@@ -12587,10 +12482,10 @@
       <c r="U80" s="23" t="n"/>
       <c r="V80" s="30" t="n"/>
     </row>
-    <row r="81" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A81" s="91" t="n"/>
-      <c r="B81" s="92" t="n"/>
-      <c r="C81" s="92" t="n"/>
+    <row r="81" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A81" s="59" t="n"/>
+      <c r="B81" s="62" t="n"/>
+      <c r="C81" s="62" t="n"/>
       <c r="D81" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12645,10 +12540,10 @@
       <c r="U81" s="23" t="n"/>
       <c r="V81" s="30" t="n"/>
     </row>
-    <row r="82" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A82" s="91" t="n"/>
-      <c r="B82" s="92" t="n"/>
-      <c r="C82" s="92" t="n"/>
+    <row r="82" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A82" s="59" t="n"/>
+      <c r="B82" s="62" t="n"/>
+      <c r="C82" s="62" t="n"/>
       <c r="D82" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -12703,10 +12598,10 @@
       <c r="U82" s="23" t="n"/>
       <c r="V82" s="30" t="n"/>
     </row>
-    <row r="83" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A83" s="91" t="n"/>
-      <c r="B83" s="92" t="n"/>
-      <c r="C83" s="92" t="n"/>
+    <row r="83" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A83" s="59" t="n"/>
+      <c r="B83" s="62" t="n"/>
+      <c r="C83" s="62" t="n"/>
       <c r="D83" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -12761,10 +12656,10 @@
       <c r="U83" s="23" t="n"/>
       <c r="V83" s="30" t="n"/>
     </row>
-    <row r="84" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A84" s="93" t="n"/>
-      <c r="B84" s="94" t="n"/>
-      <c r="C84" s="94" t="n"/>
+    <row r="84" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A84" s="60" t="n"/>
+      <c r="B84" s="63" t="n"/>
+      <c r="C84" s="63" t="n"/>
       <c r="D84" s="25" t="inlineStr">
         <is>
           <t>7 회</t>
@@ -12819,16 +12714,16 @@
       <c r="U84" s="28" t="n"/>
       <c r="V84" s="31" t="n"/>
     </row>
-    <row r="85" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A85" s="89" t="n">
+    <row r="85" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A85" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="B85" s="90" t="inlineStr">
+      <c r="B85" s="61" t="inlineStr">
         <is>
           <t>김태영</t>
         </is>
       </c>
-      <c r="C85" s="90" t="n">
+      <c r="C85" s="61" t="n">
         <v>7</v>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -12885,10 +12780,10 @@
       <c r="U85" s="23" t="n"/>
       <c r="V85" s="24" t="n"/>
     </row>
-    <row r="86" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A86" s="91" t="n"/>
-      <c r="B86" s="92" t="n"/>
-      <c r="C86" s="92" t="n"/>
+    <row r="86" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A86" s="59" t="n"/>
+      <c r="B86" s="62" t="n"/>
+      <c r="C86" s="62" t="n"/>
       <c r="D86" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -12943,10 +12838,10 @@
       <c r="U86" s="23" t="n"/>
       <c r="V86" s="24" t="n"/>
     </row>
-    <row r="87" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A87" s="91" t="n"/>
-      <c r="B87" s="92" t="n"/>
-      <c r="C87" s="92" t="n"/>
+    <row r="87" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A87" s="59" t="n"/>
+      <c r="B87" s="62" t="n"/>
+      <c r="C87" s="62" t="n"/>
       <c r="D87" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -13001,10 +12896,10 @@
       <c r="U87" s="23" t="n"/>
       <c r="V87" s="24" t="n"/>
     </row>
-    <row r="88" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A88" s="91" t="n"/>
-      <c r="B88" s="92" t="n"/>
-      <c r="C88" s="92" t="n"/>
+    <row r="88" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A88" s="59" t="n"/>
+      <c r="B88" s="62" t="n"/>
+      <c r="C88" s="62" t="n"/>
       <c r="D88" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -13059,10 +12954,10 @@
       <c r="U88" s="23" t="n"/>
       <c r="V88" s="24" t="n"/>
     </row>
-    <row r="89" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A89" s="91" t="n"/>
-      <c r="B89" s="92" t="n"/>
-      <c r="C89" s="92" t="n"/>
+    <row r="89" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A89" s="59" t="n"/>
+      <c r="B89" s="62" t="n"/>
+      <c r="C89" s="62" t="n"/>
       <c r="D89" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -13117,10 +13012,10 @@
       <c r="U89" s="23" t="n"/>
       <c r="V89" s="24" t="n"/>
     </row>
-    <row r="90" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A90" s="91" t="n"/>
-      <c r="B90" s="92" t="n"/>
-      <c r="C90" s="92" t="n"/>
+    <row r="90" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A90" s="59" t="n"/>
+      <c r="B90" s="62" t="n"/>
+      <c r="C90" s="62" t="n"/>
       <c r="D90" s="20" t="inlineStr">
         <is>
           <t>7 회</t>
@@ -13175,10 +13070,10 @@
       <c r="U90" s="23" t="n"/>
       <c r="V90" s="24" t="n"/>
     </row>
-    <row r="91" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A91" s="93" t="n"/>
-      <c r="B91" s="94" t="n"/>
-      <c r="C91" s="94" t="n"/>
+    <row r="91" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A91" s="60" t="n"/>
+      <c r="B91" s="63" t="n"/>
+      <c r="C91" s="63" t="n"/>
       <c r="D91" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -13233,16 +13128,16 @@
       <c r="U91" s="28" t="n"/>
       <c r="V91" s="29" t="n"/>
     </row>
-    <row r="92" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A92" s="89" t="n">
+    <row r="92" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A92" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="B92" s="90" t="inlineStr">
+      <c r="B92" s="61" t="inlineStr">
         <is>
           <t>양영선</t>
         </is>
       </c>
-      <c r="C92" s="90" t="n">
+      <c r="C92" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -13299,10 +13194,10 @@
       <c r="U92" s="23" t="n"/>
       <c r="V92" s="24" t="n"/>
     </row>
-    <row r="93" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A93" s="91" t="n"/>
-      <c r="B93" s="92" t="n"/>
-      <c r="C93" s="92" t="n"/>
+    <row r="93" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A93" s="59" t="n"/>
+      <c r="B93" s="62" t="n"/>
+      <c r="C93" s="62" t="n"/>
       <c r="D93" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -13357,10 +13252,10 @@
       <c r="U93" s="23" t="n"/>
       <c r="V93" s="24" t="n"/>
     </row>
-    <row r="94" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A94" s="91" t="n"/>
-      <c r="B94" s="92" t="n"/>
-      <c r="C94" s="92" t="n"/>
+    <row r="94" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A94" s="59" t="n"/>
+      <c r="B94" s="62" t="n"/>
+      <c r="C94" s="62" t="n"/>
       <c r="D94" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -13415,10 +13310,10 @@
       <c r="U94" s="23" t="n"/>
       <c r="V94" s="24" t="n"/>
     </row>
-    <row r="95" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A95" s="93" t="n"/>
-      <c r="B95" s="94" t="n"/>
-      <c r="C95" s="94" t="n"/>
+    <row r="95" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A95" s="60" t="n"/>
+      <c r="B95" s="63" t="n"/>
+      <c r="C95" s="63" t="n"/>
       <c r="D95" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -13473,16 +13368,16 @@
       <c r="U95" s="28" t="n"/>
       <c r="V95" s="29" t="n"/>
     </row>
-    <row r="96" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A96" s="89" t="n">
+    <row r="96" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A96" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="B96" s="90" t="inlineStr">
+      <c r="B96" s="61" t="inlineStr">
         <is>
           <t>장진석</t>
         </is>
       </c>
-      <c r="C96" s="90" t="n">
+      <c r="C96" s="61" t="n">
         <v>3</v>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -13539,10 +13434,10 @@
       <c r="U96" s="23" t="n"/>
       <c r="V96" s="24" t="n"/>
     </row>
-    <row r="97" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A97" s="91" t="n"/>
-      <c r="B97" s="92" t="n"/>
-      <c r="C97" s="92" t="n"/>
+    <row r="97" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A97" s="59" t="n"/>
+      <c r="B97" s="62" t="n"/>
+      <c r="C97" s="62" t="n"/>
       <c r="D97" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -13597,10 +13492,10 @@
       <c r="U97" s="23" t="n"/>
       <c r="V97" s="24" t="n"/>
     </row>
-    <row r="98" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A98" s="93" t="n"/>
-      <c r="B98" s="94" t="n"/>
-      <c r="C98" s="94" t="n"/>
+    <row r="98" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A98" s="60" t="n"/>
+      <c r="B98" s="63" t="n"/>
+      <c r="C98" s="63" t="n"/>
       <c r="D98" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -13655,31 +13550,31 @@
       <c r="U98" s="23" t="n"/>
       <c r="V98" s="29" t="n"/>
     </row>
-    <row r="99" ht="50.25" customHeight="1" s="80" thickTop="1"/>
-    <row r="100" ht="51" customHeight="1" s="80"/>
-    <row r="101" ht="50.25" customHeight="1" s="80"/>
-    <row r="102" ht="50.25" customHeight="1" s="80"/>
-    <row r="103" ht="50.25" customHeight="1" s="80"/>
-    <row r="104" ht="50.25" customHeight="1" s="80"/>
-    <row r="105" ht="50.25" customHeight="1" s="80"/>
-    <row r="106" ht="51" customHeight="1" s="80"/>
-    <row r="107" ht="50.25" customHeight="1" s="80"/>
-    <row r="108" ht="50.25" customHeight="1" s="80"/>
-    <row r="109" ht="50.25" customHeight="1" s="80"/>
-    <row r="110" ht="50.25" customHeight="1" s="80"/>
-    <row r="111" ht="50.25" customHeight="1" s="80"/>
-    <row r="112" ht="51" customHeight="1" s="80"/>
-    <row r="113" ht="50.25" customHeight="1" s="80"/>
-    <row r="114" ht="50.25" customHeight="1" s="80"/>
-    <row r="115" ht="50.25" customHeight="1" s="80"/>
-    <row r="116" ht="50.25" customHeight="1" s="80"/>
-    <row r="117" ht="50.25" customHeight="1" s="80"/>
-    <row r="118" ht="51" customHeight="1" s="80"/>
-    <row r="119" ht="50.25" customHeight="1" s="80"/>
-    <row r="120" ht="50.25" customHeight="1" s="80"/>
-    <row r="121" ht="50.25" customHeight="1" s="80"/>
-    <row r="122" ht="50.25" customHeight="1" s="80"/>
-    <row r="123" ht="17.25" customHeight="1" s="80"/>
+    <row r="99" ht="50.25" customHeight="1" s="73" thickTop="1"/>
+    <row r="100" ht="51" customHeight="1" s="73"/>
+    <row r="101" ht="50.25" customHeight="1" s="73"/>
+    <row r="102" ht="50.25" customHeight="1" s="73"/>
+    <row r="103" ht="50.25" customHeight="1" s="73"/>
+    <row r="104" ht="50.25" customHeight="1" s="73"/>
+    <row r="105" ht="50.25" customHeight="1" s="73"/>
+    <row r="106" ht="51" customHeight="1" s="73"/>
+    <row r="107" ht="50.25" customHeight="1" s="73"/>
+    <row r="108" ht="50.25" customHeight="1" s="73"/>
+    <row r="109" ht="50.25" customHeight="1" s="73"/>
+    <row r="110" ht="50.25" customHeight="1" s="73"/>
+    <row r="111" ht="50.25" customHeight="1" s="73"/>
+    <row r="112" ht="51" customHeight="1" s="73"/>
+    <row r="113" ht="50.25" customHeight="1" s="73"/>
+    <row r="114" ht="50.25" customHeight="1" s="73"/>
+    <row r="115" ht="50.25" customHeight="1" s="73"/>
+    <row r="116" ht="50.25" customHeight="1" s="73"/>
+    <row r="117" ht="50.25" customHeight="1" s="73"/>
+    <row r="118" ht="51" customHeight="1" s="73"/>
+    <row r="119" ht="50.25" customHeight="1" s="73"/>
+    <row r="120" ht="50.25" customHeight="1" s="73"/>
+    <row r="121" ht="50.25" customHeight="1" s="73"/>
+    <row r="122" ht="50.25" customHeight="1" s="73"/>
+    <row r="123" ht="17.25" customHeight="1" s="73"/>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="A9:A14"/>
@@ -13714,17 +13609,17 @@
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A21:A26"/>
     <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C21:C26"/>
     <mergeCell ref="A55:A60"/>
-    <mergeCell ref="C21:C26"/>
     <mergeCell ref="B92:B95"/>
     <mergeCell ref="B85:B91"/>
     <mergeCell ref="A33:A38"/>
     <mergeCell ref="A45:A49"/>
+    <mergeCell ref="C27:C32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="C67:C72"/>
     <mergeCell ref="B15:B20"/>
-    <mergeCell ref="B33:B38"/>
-    <mergeCell ref="C27:C32"/>
-    <mergeCell ref="C67:C72"/>
-    <mergeCell ref="C45:C49"/>
     <mergeCell ref="C61:C66"/>
     <mergeCell ref="C73:C77"/>
     <mergeCell ref="C39:C44"/>
@@ -13752,51 +13647,51 @@
   <dimension ref="A1:V118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="80" thickBot="1">
-      <c r="A1" s="81" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1" s="73" thickBot="1">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>분반정보</t>
         </is>
       </c>
-      <c r="B1" s="82" t="n"/>
-      <c r="C1" s="83" t="n"/>
-      <c r="D1" s="84" t="inlineStr">
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="68" t="inlineStr">
         <is>
           <t>학생정보</t>
         </is>
       </c>
-      <c r="E1" s="82" t="n"/>
-      <c r="F1" s="82" t="n"/>
-      <c r="G1" s="82" t="n"/>
-      <c r="H1" s="82" t="n"/>
-      <c r="I1" s="82" t="n"/>
-      <c r="J1" s="83" t="n"/>
-      <c r="K1" s="85" t="inlineStr">
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="67" t="n"/>
+      <c r="K1" s="66" t="inlineStr">
         <is>
           <t>학부모정보</t>
         </is>
       </c>
-      <c r="L1" s="83" t="n"/>
-      <c r="M1" s="86" t="inlineStr">
+      <c r="L1" s="67" t="n"/>
+      <c r="M1" s="71" t="inlineStr">
         <is>
           <t>출석부</t>
         </is>
       </c>
-      <c r="N1" s="82" t="n"/>
-      <c r="O1" s="82" t="n"/>
-      <c r="P1" s="82" t="n"/>
-      <c r="Q1" s="82" t="n"/>
-      <c r="R1" s="82" t="n"/>
-      <c r="S1" s="82" t="n"/>
-      <c r="T1" s="82" t="n"/>
-      <c r="U1" s="83" t="n"/>
-      <c r="V1" s="87" t="inlineStr">
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="67" t="n"/>
+      <c r="V1" s="64" t="inlineStr">
         <is>
           <t>USB포트유무</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="80" thickBot="1">
+    <row r="2" ht="33.75" customHeight="1" s="73" thickBot="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
           <t>분반</t>
@@ -13902,18 +13797,18 @@
           <t>이슈사항</t>
         </is>
       </c>
-      <c r="V2" s="88" t="n"/>
-    </row>
-    <row r="3" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A3" s="89" t="n">
+      <c r="V2" s="65" t="n"/>
+    </row>
+    <row r="3" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A3" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="90" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>지주희</t>
         </is>
       </c>
-      <c r="C3" s="90" t="n">
+      <c r="C3" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D3" s="20" t="inlineStr">
@@ -13970,10 +13865,10 @@
       <c r="U3" s="23" t="n"/>
       <c r="V3" s="24" t="n"/>
     </row>
-    <row r="4" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A4" s="91" t="n"/>
-      <c r="B4" s="92" t="n"/>
-      <c r="C4" s="92" t="n"/>
+    <row r="4" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A4" s="59" t="n"/>
+      <c r="B4" s="62" t="n"/>
+      <c r="C4" s="62" t="n"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14028,10 +13923,10 @@
       <c r="U4" s="23" t="n"/>
       <c r="V4" s="24" t="n"/>
     </row>
-    <row r="5" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A5" s="91" t="n"/>
-      <c r="B5" s="92" t="n"/>
-      <c r="C5" s="92" t="n"/>
+    <row r="5" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A5" s="59" t="n"/>
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -14086,10 +13981,10 @@
       <c r="U5" s="23" t="n"/>
       <c r="V5" s="24" t="n"/>
     </row>
-    <row r="6" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A6" s="91" t="n"/>
-      <c r="B6" s="92" t="n"/>
-      <c r="C6" s="92" t="n"/>
+    <row r="6" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A6" s="59" t="n"/>
+      <c r="B6" s="62" t="n"/>
+      <c r="C6" s="62" t="n"/>
       <c r="D6" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14144,10 +14039,10 @@
       <c r="U6" s="23" t="n"/>
       <c r="V6" s="24" t="n"/>
     </row>
-    <row r="7" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A7" s="91" t="n"/>
-      <c r="B7" s="92" t="n"/>
-      <c r="C7" s="92" t="n"/>
+    <row r="7" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A7" s="59" t="n"/>
+      <c r="B7" s="62" t="n"/>
+      <c r="C7" s="62" t="n"/>
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -14202,10 +14097,10 @@
       <c r="U7" s="23" t="n"/>
       <c r="V7" s="24" t="n"/>
     </row>
-    <row r="8" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A8" s="93" t="n"/>
-      <c r="B8" s="94" t="n"/>
-      <c r="C8" s="94" t="n"/>
+    <row r="8" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A8" s="60" t="n"/>
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="63" t="n"/>
       <c r="D8" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14260,16 +14155,16 @@
       <c r="U8" s="28" t="n"/>
       <c r="V8" s="29" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A9" s="89" t="n">
+    <row r="9" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A9" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="90" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>조지은</t>
         </is>
       </c>
-      <c r="C9" s="90" t="n">
+      <c r="C9" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14326,10 +14221,10 @@
       <c r="U9" s="23" t="n"/>
       <c r="V9" s="24" t="n"/>
     </row>
-    <row r="10" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A10" s="91" t="n"/>
-      <c r="B10" s="92" t="n"/>
-      <c r="C10" s="92" t="n"/>
+    <row r="10" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A10" s="59" t="n"/>
+      <c r="B10" s="62" t="n"/>
+      <c r="C10" s="62" t="n"/>
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14384,10 +14279,10 @@
       <c r="U10" s="23" t="n"/>
       <c r="V10" s="24" t="n"/>
     </row>
-    <row r="11" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A11" s="91" t="n"/>
-      <c r="B11" s="92" t="n"/>
-      <c r="C11" s="92" t="n"/>
+    <row r="11" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A11" s="59" t="n"/>
+      <c r="B11" s="62" t="n"/>
+      <c r="C11" s="62" t="n"/>
       <c r="D11" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14442,10 +14337,10 @@
       <c r="U11" s="23" t="n"/>
       <c r="V11" s="24" t="n"/>
     </row>
-    <row r="12" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A12" s="91" t="n"/>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
+    <row r="12" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A12" s="59" t="n"/>
+      <c r="B12" s="62" t="n"/>
+      <c r="C12" s="62" t="n"/>
       <c r="D12" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -14500,10 +14395,10 @@
       <c r="U12" s="23" t="n"/>
       <c r="V12" s="24" t="n"/>
     </row>
-    <row r="13" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A13" s="91" t="n"/>
-      <c r="B13" s="92" t="n"/>
-      <c r="C13" s="92" t="n"/>
+    <row r="13" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A13" s="59" t="n"/>
+      <c r="B13" s="62" t="n"/>
+      <c r="C13" s="62" t="n"/>
       <c r="D13" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -14558,10 +14453,10 @@
       <c r="U13" s="23" t="n"/>
       <c r="V13" s="24" t="n"/>
     </row>
-    <row r="14" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A14" s="93" t="n"/>
-      <c r="B14" s="94" t="n"/>
-      <c r="C14" s="94" t="n"/>
+    <row r="14" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A14" s="60" t="n"/>
+      <c r="B14" s="63" t="n"/>
+      <c r="C14" s="63" t="n"/>
       <c r="D14" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -14616,16 +14511,16 @@
       <c r="U14" s="28" t="n"/>
       <c r="V14" s="29" t="n"/>
     </row>
-    <row r="15" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A15" s="89" t="n">
+    <row r="15" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A15" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="90" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>곽미영</t>
         </is>
       </c>
-      <c r="C15" s="90" t="n">
+      <c r="C15" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -14682,10 +14577,10 @@
       <c r="U15" s="23" t="n"/>
       <c r="V15" s="24" t="n"/>
     </row>
-    <row r="16" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A16" s="91" t="n"/>
-      <c r="B16" s="92" t="n"/>
-      <c r="C16" s="92" t="n"/>
+    <row r="16" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A16" s="59" t="n"/>
+      <c r="B16" s="62" t="n"/>
+      <c r="C16" s="62" t="n"/>
       <c r="D16" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14740,10 +14635,10 @@
       <c r="U16" s="23" t="n"/>
       <c r="V16" s="24" t="n"/>
     </row>
-    <row r="17" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A17" s="91" t="n"/>
-      <c r="B17" s="92" t="n"/>
-      <c r="C17" s="92" t="n"/>
+    <row r="17" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A17" s="59" t="n"/>
+      <c r="B17" s="62" t="n"/>
+      <c r="C17" s="62" t="n"/>
       <c r="D17" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -14798,10 +14693,10 @@
       <c r="U17" s="23" t="n"/>
       <c r="V17" s="24" t="n"/>
     </row>
-    <row r="18" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A18" s="91" t="n"/>
-      <c r="B18" s="92" t="n"/>
-      <c r="C18" s="92" t="n"/>
+    <row r="18" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A18" s="59" t="n"/>
+      <c r="B18" s="62" t="n"/>
+      <c r="C18" s="62" t="n"/>
       <c r="D18" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14856,10 +14751,10 @@
       <c r="U18" s="23" t="n"/>
       <c r="V18" s="24" t="n"/>
     </row>
-    <row r="19" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A19" s="91" t="n"/>
-      <c r="B19" s="92" t="n"/>
-      <c r="C19" s="92" t="n"/>
+    <row r="19" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A19" s="59" t="n"/>
+      <c r="B19" s="62" t="n"/>
+      <c r="C19" s="62" t="n"/>
       <c r="D19" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14914,10 +14809,10 @@
       <c r="U19" s="23" t="n"/>
       <c r="V19" s="24" t="n"/>
     </row>
-    <row r="20" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A20" s="93" t="n"/>
-      <c r="B20" s="94" t="n"/>
-      <c r="C20" s="94" t="n"/>
+    <row r="20" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A20" s="60" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="63" t="n"/>
       <c r="D20" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -14972,16 +14867,16 @@
       <c r="U20" s="28" t="n"/>
       <c r="V20" s="29" t="n"/>
     </row>
-    <row r="21" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A21" s="89" t="n">
+    <row r="21" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A21" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>최말여</t>
         </is>
       </c>
-      <c r="C21" s="90" t="n">
+      <c r="C21" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -15038,10 +14933,10 @@
       <c r="U21" s="23" t="n"/>
       <c r="V21" s="24" t="n"/>
     </row>
-    <row r="22" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A22" s="91" t="n"/>
-      <c r="B22" s="92" t="n"/>
-      <c r="C22" s="92" t="n"/>
+    <row r="22" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A22" s="59" t="n"/>
+      <c r="B22" s="62" t="n"/>
+      <c r="C22" s="62" t="n"/>
       <c r="D22" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -15096,10 +14991,10 @@
       <c r="U22" s="23" t="n"/>
       <c r="V22" s="24" t="n"/>
     </row>
-    <row r="23" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A23" s="91" t="n"/>
-      <c r="B23" s="92" t="n"/>
-      <c r="C23" s="92" t="n"/>
+    <row r="23" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A23" s="59" t="n"/>
+      <c r="B23" s="62" t="n"/>
+      <c r="C23" s="62" t="n"/>
       <c r="D23" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -15154,10 +15049,10 @@
       <c r="U23" s="23" t="n"/>
       <c r="V23" s="24" t="n"/>
     </row>
-    <row r="24" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A24" s="91" t="n"/>
-      <c r="B24" s="92" t="n"/>
-      <c r="C24" s="92" t="n"/>
+    <row r="24" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A24" s="59" t="n"/>
+      <c r="B24" s="62" t="n"/>
+      <c r="C24" s="62" t="n"/>
       <c r="D24" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -15212,10 +15107,10 @@
       <c r="U24" s="23" t="n"/>
       <c r="V24" s="24" t="n"/>
     </row>
-    <row r="25" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A25" s="91" t="n"/>
-      <c r="B25" s="92" t="n"/>
-      <c r="C25" s="92" t="n"/>
+    <row r="25" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A25" s="59" t="n"/>
+      <c r="B25" s="62" t="n"/>
+      <c r="C25" s="62" t="n"/>
       <c r="D25" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -15270,10 +15165,10 @@
       <c r="U25" s="23" t="n"/>
       <c r="V25" s="24" t="n"/>
     </row>
-    <row r="26" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A26" s="93" t="n"/>
-      <c r="B26" s="94" t="n"/>
-      <c r="C26" s="94" t="n"/>
+    <row r="26" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A26" s="60" t="n"/>
+      <c r="B26" s="63" t="n"/>
+      <c r="C26" s="63" t="n"/>
       <c r="D26" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -15328,16 +15223,16 @@
       <c r="U26" s="28" t="n"/>
       <c r="V26" s="29" t="n"/>
     </row>
-    <row r="27" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A27" s="89" t="n">
+    <row r="27" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A27" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="90" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>박현주</t>
         </is>
       </c>
-      <c r="C27" s="90" t="n">
+      <c r="C27" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -15394,10 +15289,10 @@
       <c r="U27" s="23" t="n"/>
       <c r="V27" s="24" t="n"/>
     </row>
-    <row r="28" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A28" s="91" t="n"/>
-      <c r="B28" s="92" t="n"/>
-      <c r="C28" s="92" t="n"/>
+    <row r="28" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A28" s="59" t="n"/>
+      <c r="B28" s="62" t="n"/>
+      <c r="C28" s="62" t="n"/>
       <c r="D28" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -15452,10 +15347,10 @@
       <c r="U28" s="23" t="n"/>
       <c r="V28" s="24" t="n"/>
     </row>
-    <row r="29" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A29" s="91" t="n"/>
-      <c r="B29" s="92" t="n"/>
-      <c r="C29" s="92" t="n"/>
+    <row r="29" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A29" s="59" t="n"/>
+      <c r="B29" s="62" t="n"/>
+      <c r="C29" s="62" t="n"/>
       <c r="D29" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -15510,10 +15405,10 @@
       <c r="U29" s="23" t="n"/>
       <c r="V29" s="24" t="n"/>
     </row>
-    <row r="30" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A30" s="91" t="n"/>
-      <c r="B30" s="92" t="n"/>
-      <c r="C30" s="92" t="n"/>
+    <row r="30" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A30" s="59" t="n"/>
+      <c r="B30" s="62" t="n"/>
+      <c r="C30" s="62" t="n"/>
       <c r="D30" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -15568,10 +15463,10 @@
       <c r="U30" s="23" t="n"/>
       <c r="V30" s="24" t="n"/>
     </row>
-    <row r="31" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A31" s="91" t="n"/>
-      <c r="B31" s="92" t="n"/>
-      <c r="C31" s="92" t="n"/>
+    <row r="31" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A31" s="59" t="n"/>
+      <c r="B31" s="62" t="n"/>
+      <c r="C31" s="62" t="n"/>
       <c r="D31" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -15626,10 +15521,10 @@
       <c r="U31" s="23" t="n"/>
       <c r="V31" s="24" t="n"/>
     </row>
-    <row r="32" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A32" s="93" t="n"/>
-      <c r="B32" s="94" t="n"/>
-      <c r="C32" s="94" t="n"/>
+    <row r="32" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A32" s="60" t="n"/>
+      <c r="B32" s="63" t="n"/>
+      <c r="C32" s="63" t="n"/>
       <c r="D32" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -15684,16 +15579,16 @@
       <c r="U32" s="28" t="n"/>
       <c r="V32" s="29" t="n"/>
     </row>
-    <row r="33" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A33" s="89" t="n">
+    <row r="33" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A33" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="90" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>김경진</t>
         </is>
       </c>
-      <c r="C33" s="90" t="n">
+      <c r="C33" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -15750,10 +15645,10 @@
       <c r="U33" s="23" t="n"/>
       <c r="V33" s="24" t="n"/>
     </row>
-    <row r="34" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A34" s="91" t="n"/>
-      <c r="B34" s="92" t="n"/>
-      <c r="C34" s="92" t="n"/>
+    <row r="34" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A34" s="59" t="n"/>
+      <c r="B34" s="62" t="n"/>
+      <c r="C34" s="62" t="n"/>
       <c r="D34" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -15808,10 +15703,10 @@
       <c r="U34" s="23" t="n"/>
       <c r="V34" s="24" t="n"/>
     </row>
-    <row r="35" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A35" s="91" t="n"/>
-      <c r="B35" s="92" t="n"/>
-      <c r="C35" s="92" t="n"/>
+    <row r="35" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A35" s="59" t="n"/>
+      <c r="B35" s="62" t="n"/>
+      <c r="C35" s="62" t="n"/>
       <c r="D35" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -15866,10 +15761,10 @@
       <c r="U35" s="23" t="n"/>
       <c r="V35" s="24" t="n"/>
     </row>
-    <row r="36" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A36" s="91" t="n"/>
-      <c r="B36" s="92" t="n"/>
-      <c r="C36" s="92" t="n"/>
+    <row r="36" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A36" s="59" t="n"/>
+      <c r="B36" s="62" t="n"/>
+      <c r="C36" s="62" t="n"/>
       <c r="D36" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -15924,10 +15819,10 @@
       <c r="U36" s="23" t="n"/>
       <c r="V36" s="24" t="n"/>
     </row>
-    <row r="37" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A37" s="91" t="n"/>
-      <c r="B37" s="92" t="n"/>
-      <c r="C37" s="92" t="n"/>
+    <row r="37" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A37" s="59" t="n"/>
+      <c r="B37" s="62" t="n"/>
+      <c r="C37" s="62" t="n"/>
       <c r="D37" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -15982,10 +15877,10 @@
       <c r="U37" s="23" t="n"/>
       <c r="V37" s="24" t="n"/>
     </row>
-    <row r="38" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A38" s="93" t="n"/>
-      <c r="B38" s="94" t="n"/>
-      <c r="C38" s="94" t="n"/>
+    <row r="38" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A38" s="60" t="n"/>
+      <c r="B38" s="63" t="n"/>
+      <c r="C38" s="63" t="n"/>
       <c r="D38" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16040,16 +15935,16 @@
       <c r="U38" s="28" t="n"/>
       <c r="V38" s="29" t="n"/>
     </row>
-    <row r="39" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A39" s="89" t="n">
+    <row r="39" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A39" s="58" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="90" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>이주원</t>
         </is>
       </c>
-      <c r="C39" s="90" t="n">
+      <c r="C39" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -16106,10 +16001,10 @@
       <c r="U39" s="23" t="n"/>
       <c r="V39" s="30" t="n"/>
     </row>
-    <row r="40" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A40" s="91" t="n"/>
-      <c r="B40" s="92" t="n"/>
-      <c r="C40" s="92" t="n"/>
+    <row r="40" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A40" s="59" t="n"/>
+      <c r="B40" s="62" t="n"/>
+      <c r="C40" s="62" t="n"/>
       <c r="D40" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16164,10 +16059,10 @@
       <c r="U40" s="23" t="n"/>
       <c r="V40" s="30" t="n"/>
     </row>
-    <row r="41" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A41" s="91" t="n"/>
-      <c r="B41" s="92" t="n"/>
-      <c r="C41" s="92" t="n"/>
+    <row r="41" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A41" s="59" t="n"/>
+      <c r="B41" s="62" t="n"/>
+      <c r="C41" s="62" t="n"/>
       <c r="D41" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16222,10 +16117,10 @@
       <c r="U41" s="23" t="n"/>
       <c r="V41" s="30" t="n"/>
     </row>
-    <row r="42" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A42" s="91" t="n"/>
-      <c r="B42" s="92" t="n"/>
-      <c r="C42" s="92" t="n"/>
+    <row r="42" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A42" s="59" t="n"/>
+      <c r="B42" s="62" t="n"/>
+      <c r="C42" s="62" t="n"/>
       <c r="D42" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -16280,10 +16175,10 @@
       <c r="U42" s="53" t="n"/>
       <c r="V42" s="30" t="n"/>
     </row>
-    <row r="43" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A43" s="91" t="n"/>
-      <c r="B43" s="92" t="n"/>
-      <c r="C43" s="92" t="n"/>
+    <row r="43" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A43" s="59" t="n"/>
+      <c r="B43" s="62" t="n"/>
+      <c r="C43" s="62" t="n"/>
       <c r="D43" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -16338,10 +16233,10 @@
       <c r="U43" s="23" t="n"/>
       <c r="V43" s="30" t="n"/>
     </row>
-    <row r="44" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A44" s="93" t="n"/>
-      <c r="B44" s="94" t="n"/>
-      <c r="C44" s="94" t="n"/>
+    <row r="44" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A44" s="60" t="n"/>
+      <c r="B44" s="63" t="n"/>
+      <c r="C44" s="63" t="n"/>
       <c r="D44" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16396,16 +16291,16 @@
       <c r="U44" s="28" t="n"/>
       <c r="V44" s="31" t="n"/>
     </row>
-    <row r="45" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A45" s="89" t="n">
+    <row r="45" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A45" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="B45" s="90" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>장은영</t>
         </is>
       </c>
-      <c r="C45" s="90" t="n">
+      <c r="C45" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -16462,10 +16357,10 @@
       <c r="U45" s="23" t="n"/>
       <c r="V45" s="24" t="n"/>
     </row>
-    <row r="46" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A46" s="91" t="n"/>
-      <c r="B46" s="92" t="n"/>
-      <c r="C46" s="92" t="n"/>
+    <row r="46" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A46" s="59" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
       <c r="D46" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -16520,10 +16415,10 @@
       <c r="U46" s="23" t="n"/>
       <c r="V46" s="24" t="n"/>
     </row>
-    <row r="47" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A47" s="91" t="n"/>
-      <c r="B47" s="92" t="n"/>
-      <c r="C47" s="92" t="n"/>
+    <row r="47" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
       <c r="D47" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16578,10 +16473,10 @@
       <c r="U47" s="23" t="n"/>
       <c r="V47" s="24" t="n"/>
     </row>
-    <row r="48" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A48" s="91" t="n"/>
-      <c r="B48" s="92" t="n"/>
-      <c r="C48" s="92" t="n"/>
+    <row r="48" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
       <c r="D48" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16636,10 +16531,10 @@
       <c r="U48" s="23" t="n"/>
       <c r="V48" s="24" t="n"/>
     </row>
-    <row r="49" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A49" s="91" t="n"/>
-      <c r="B49" s="92" t="n"/>
-      <c r="C49" s="92" t="n"/>
+    <row r="49" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A49" s="59" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
       <c r="D49" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -16694,10 +16589,10 @@
       <c r="U49" s="23" t="n"/>
       <c r="V49" s="24" t="n"/>
     </row>
-    <row r="50" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A50" s="93" t="n"/>
-      <c r="B50" s="94" t="n"/>
-      <c r="C50" s="94" t="n"/>
+    <row r="50" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A50" s="60" t="n"/>
+      <c r="B50" s="63" t="n"/>
+      <c r="C50" s="63" t="n"/>
       <c r="D50" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16752,16 +16647,16 @@
       <c r="U50" s="28" t="n"/>
       <c r="V50" s="29" t="n"/>
     </row>
-    <row r="51" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A51" s="89" t="n">
+    <row r="51" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A51" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="90" t="inlineStr">
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>황수리</t>
         </is>
       </c>
-      <c r="C51" s="90" t="n">
+      <c r="C51" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -16818,10 +16713,10 @@
       <c r="U51" s="23" t="n"/>
       <c r="V51" s="24" t="n"/>
     </row>
-    <row r="52" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A52" s="91" t="n"/>
-      <c r="B52" s="92" t="n"/>
-      <c r="C52" s="92" t="n"/>
+    <row r="52" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A52" s="59" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
       <c r="D52" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -16876,10 +16771,10 @@
       <c r="U52" s="23" t="n"/>
       <c r="V52" s="24" t="n"/>
     </row>
-    <row r="53" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A53" s="91" t="n"/>
-      <c r="B53" s="92" t="n"/>
-      <c r="C53" s="92" t="n"/>
+    <row r="53" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A53" s="59" t="n"/>
+      <c r="B53" s="62" t="n"/>
+      <c r="C53" s="62" t="n"/>
       <c r="D53" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -16934,10 +16829,10 @@
       <c r="U53" s="54" t="n"/>
       <c r="V53" s="24" t="n"/>
     </row>
-    <row r="54" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A54" s="91" t="n"/>
-      <c r="B54" s="92" t="n"/>
-      <c r="C54" s="92" t="n"/>
+    <row r="54" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A54" s="59" t="n"/>
+      <c r="B54" s="62" t="n"/>
+      <c r="C54" s="62" t="n"/>
       <c r="D54" s="34" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -16992,10 +16887,10 @@
       <c r="U54" s="23" t="n"/>
       <c r="V54" s="24" t="n"/>
     </row>
-    <row r="55" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A55" s="91" t="n"/>
-      <c r="B55" s="92" t="n"/>
-      <c r="C55" s="92" t="n"/>
+    <row r="55" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A55" s="59" t="n"/>
+      <c r="B55" s="62" t="n"/>
+      <c r="C55" s="62" t="n"/>
       <c r="D55" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -17050,10 +16945,10 @@
       <c r="U55" s="23" t="n"/>
       <c r="V55" s="24" t="n"/>
     </row>
-    <row r="56" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A56" s="93" t="n"/>
-      <c r="B56" s="94" t="n"/>
-      <c r="C56" s="94" t="n"/>
+    <row r="56" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A56" s="60" t="n"/>
+      <c r="B56" s="63" t="n"/>
+      <c r="C56" s="63" t="n"/>
       <c r="D56" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17108,16 +17003,16 @@
       <c r="U56" s="28" t="n"/>
       <c r="V56" s="29" t="n"/>
     </row>
-    <row r="57" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A57" s="89" t="n">
+    <row r="57" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A57" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="90" t="inlineStr">
+      <c r="B57" s="61" t="inlineStr">
         <is>
           <t>김현지</t>
         </is>
       </c>
-      <c r="C57" s="90" t="n">
+      <c r="C57" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -17174,10 +17069,10 @@
       <c r="U57" s="23" t="n"/>
       <c r="V57" s="24" t="n"/>
     </row>
-    <row r="58" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A58" s="91" t="n"/>
-      <c r="B58" s="92" t="n"/>
-      <c r="C58" s="92" t="n"/>
+    <row r="58" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A58" s="59" t="n"/>
+      <c r="B58" s="62" t="n"/>
+      <c r="C58" s="62" t="n"/>
       <c r="D58" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -17232,10 +17127,10 @@
       <c r="U58" s="23" t="n"/>
       <c r="V58" s="24" t="n"/>
     </row>
-    <row r="59" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A59" s="91" t="n"/>
-      <c r="B59" s="92" t="n"/>
-      <c r="C59" s="92" t="n"/>
+    <row r="59" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="62" t="n"/>
+      <c r="C59" s="62" t="n"/>
       <c r="D59" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -17290,10 +17185,10 @@
       <c r="U59" s="23" t="n"/>
       <c r="V59" s="24" t="n"/>
     </row>
-    <row r="60" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A60" s="91" t="n"/>
-      <c r="B60" s="92" t="n"/>
-      <c r="C60" s="92" t="n"/>
+    <row r="60" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A60" s="59" t="n"/>
+      <c r="B60" s="62" t="n"/>
+      <c r="C60" s="62" t="n"/>
       <c r="D60" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -17348,10 +17243,10 @@
       <c r="U60" s="23" t="n"/>
       <c r="V60" s="24" t="n"/>
     </row>
-    <row r="61" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A61" s="91" t="n"/>
-      <c r="B61" s="92" t="n"/>
-      <c r="C61" s="92" t="n"/>
+    <row r="61" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A61" s="59" t="n"/>
+      <c r="B61" s="62" t="n"/>
+      <c r="C61" s="62" t="n"/>
       <c r="D61" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17406,10 +17301,10 @@
       <c r="U61" s="23" t="n"/>
       <c r="V61" s="24" t="n"/>
     </row>
-    <row r="62" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A62" s="93" t="n"/>
-      <c r="B62" s="94" t="n"/>
-      <c r="C62" s="94" t="n"/>
+    <row r="62" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A62" s="60" t="n"/>
+      <c r="B62" s="63" t="n"/>
+      <c r="C62" s="63" t="n"/>
       <c r="D62" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17464,16 +17359,16 @@
       <c r="U62" s="28" t="n"/>
       <c r="V62" s="29" t="n"/>
     </row>
-    <row r="63" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A63" s="89" t="n">
+    <row r="63" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A63" s="58" t="n">
         <v>11</v>
       </c>
-      <c r="B63" s="90" t="inlineStr">
+      <c r="B63" s="61" t="inlineStr">
         <is>
           <t>안소영</t>
         </is>
       </c>
-      <c r="C63" s="90" t="n">
+      <c r="C63" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -17530,10 +17425,10 @@
       <c r="U63" s="23" t="n"/>
       <c r="V63" s="24" t="n"/>
     </row>
-    <row r="64" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A64" s="91" t="n"/>
-      <c r="B64" s="92" t="n"/>
-      <c r="C64" s="92" t="n"/>
+    <row r="64" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A64" s="59" t="n"/>
+      <c r="B64" s="62" t="n"/>
+      <c r="C64" s="62" t="n"/>
       <c r="D64" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17588,10 +17483,10 @@
       <c r="U64" s="23" t="n"/>
       <c r="V64" s="24" t="n"/>
     </row>
-    <row r="65" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A65" s="91" t="n"/>
-      <c r="B65" s="92" t="n"/>
-      <c r="C65" s="92" t="n"/>
+    <row r="65" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A65" s="59" t="n"/>
+      <c r="B65" s="62" t="n"/>
+      <c r="C65" s="62" t="n"/>
       <c r="D65" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17646,10 +17541,10 @@
       <c r="U65" s="23" t="n"/>
       <c r="V65" s="24" t="n"/>
     </row>
-    <row r="66" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A66" s="91" t="n"/>
-      <c r="B66" s="92" t="n"/>
-      <c r="C66" s="92" t="n"/>
+    <row r="66" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A66" s="59" t="n"/>
+      <c r="B66" s="62" t="n"/>
+      <c r="C66" s="62" t="n"/>
       <c r="D66" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -17704,10 +17599,10 @@
       <c r="U66" s="23" t="n"/>
       <c r="V66" s="24" t="n"/>
     </row>
-    <row r="67" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A67" s="91" t="n"/>
-      <c r="B67" s="92" t="n"/>
-      <c r="C67" s="92" t="n"/>
+    <row r="67" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A67" s="59" t="n"/>
+      <c r="B67" s="62" t="n"/>
+      <c r="C67" s="62" t="n"/>
       <c r="D67" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17762,10 +17657,10 @@
       <c r="U67" s="23" t="n"/>
       <c r="V67" s="24" t="n"/>
     </row>
-    <row r="68" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A68" s="93" t="n"/>
-      <c r="B68" s="94" t="n"/>
-      <c r="C68" s="94" t="n"/>
+    <row r="68" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A68" s="60" t="n"/>
+      <c r="B68" s="63" t="n"/>
+      <c r="C68" s="63" t="n"/>
       <c r="D68" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17820,16 +17715,16 @@
       <c r="U68" s="28" t="n"/>
       <c r="V68" s="29" t="n"/>
     </row>
-    <row r="69" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A69" s="89" t="n">
+    <row r="69" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A69" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="B69" s="90" t="inlineStr">
+      <c r="B69" s="61" t="inlineStr">
         <is>
           <t>김숙희</t>
         </is>
       </c>
-      <c r="C69" s="90" t="n">
+      <c r="C69" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -17886,10 +17781,10 @@
       <c r="U69" s="23" t="n"/>
       <c r="V69" s="30" t="n"/>
     </row>
-    <row r="70" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A70" s="91" t="n"/>
-      <c r="B70" s="92" t="n"/>
-      <c r="C70" s="92" t="n"/>
+    <row r="70" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A70" s="59" t="n"/>
+      <c r="B70" s="62" t="n"/>
+      <c r="C70" s="62" t="n"/>
       <c r="D70" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -17944,10 +17839,10 @@
       <c r="U70" s="23" t="n"/>
       <c r="V70" s="30" t="n"/>
     </row>
-    <row r="71" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A71" s="91" t="n"/>
-      <c r="B71" s="92" t="n"/>
-      <c r="C71" s="92" t="n"/>
+    <row r="71" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A71" s="59" t="n"/>
+      <c r="B71" s="62" t="n"/>
+      <c r="C71" s="62" t="n"/>
       <c r="D71" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -18002,10 +17897,10 @@
       <c r="U71" s="23" t="n"/>
       <c r="V71" s="22" t="n"/>
     </row>
-    <row r="72" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A72" s="91" t="n"/>
-      <c r="B72" s="92" t="n"/>
-      <c r="C72" s="92" t="n"/>
+    <row r="72" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A72" s="59" t="n"/>
+      <c r="B72" s="62" t="n"/>
+      <c r="C72" s="62" t="n"/>
       <c r="D72" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -18060,10 +17955,10 @@
       <c r="U72" s="23" t="n"/>
       <c r="V72" s="30" t="n"/>
     </row>
-    <row r="73" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A73" s="91" t="n"/>
-      <c r="B73" s="92" t="n"/>
-      <c r="C73" s="92" t="n"/>
+    <row r="73" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A73" s="59" t="n"/>
+      <c r="B73" s="62" t="n"/>
+      <c r="C73" s="62" t="n"/>
       <c r="D73" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -18118,10 +18013,10 @@
       <c r="U73" s="23" t="n"/>
       <c r="V73" s="30" t="n"/>
     </row>
-    <row r="74" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A74" s="93" t="n"/>
-      <c r="B74" s="94" t="n"/>
-      <c r="C74" s="94" t="n"/>
+    <row r="74" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A74" s="60" t="n"/>
+      <c r="B74" s="63" t="n"/>
+      <c r="C74" s="63" t="n"/>
       <c r="D74" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -18176,16 +18071,16 @@
       <c r="U74" s="28" t="n"/>
       <c r="V74" s="31" t="n"/>
     </row>
-    <row r="75" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A75" s="95" t="n">
+    <row r="75" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A75" s="72" t="n">
         <v>13</v>
       </c>
-      <c r="B75" s="90" t="inlineStr">
+      <c r="B75" s="61" t="inlineStr">
         <is>
           <t>박지윤</t>
         </is>
       </c>
-      <c r="C75" s="90" t="n">
+      <c r="C75" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D75" s="36" t="inlineStr">
@@ -18242,10 +18137,10 @@
       <c r="U75" s="23" t="n"/>
       <c r="V75" s="24" t="n"/>
     </row>
-    <row r="76" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A76" s="91" t="n"/>
-      <c r="B76" s="92" t="n"/>
-      <c r="C76" s="92" t="n"/>
+    <row r="76" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A76" s="59" t="n"/>
+      <c r="B76" s="62" t="n"/>
+      <c r="C76" s="62" t="n"/>
       <c r="D76" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -18300,10 +18195,10 @@
       <c r="U76" s="23" t="n"/>
       <c r="V76" s="24" t="n"/>
     </row>
-    <row r="77" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A77" s="91" t="n"/>
-      <c r="B77" s="92" t="n"/>
-      <c r="C77" s="92" t="n"/>
+    <row r="77" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A77" s="59" t="n"/>
+      <c r="B77" s="62" t="n"/>
+      <c r="C77" s="62" t="n"/>
       <c r="D77" s="20" t="inlineStr">
         <is>
           <t>6 회</t>
@@ -18358,10 +18253,10 @@
       <c r="U77" s="23" t="n"/>
       <c r="V77" s="24" t="n"/>
     </row>
-    <row r="78" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A78" s="91" t="n"/>
-      <c r="B78" s="92" t="n"/>
-      <c r="C78" s="92" t="n"/>
+    <row r="78" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A78" s="59" t="n"/>
+      <c r="B78" s="62" t="n"/>
+      <c r="C78" s="62" t="n"/>
       <c r="D78" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -18416,10 +18311,10 @@
       <c r="U78" s="23" t="n"/>
       <c r="V78" s="24" t="n"/>
     </row>
-    <row r="79" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A79" s="91" t="n"/>
-      <c r="B79" s="92" t="n"/>
-      <c r="C79" s="92" t="n"/>
+    <row r="79" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A79" s="59" t="n"/>
+      <c r="B79" s="62" t="n"/>
+      <c r="C79" s="62" t="n"/>
       <c r="D79" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -18474,10 +18369,10 @@
       <c r="U79" s="23" t="n"/>
       <c r="V79" s="24" t="n"/>
     </row>
-    <row r="80" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A80" s="93" t="n"/>
-      <c r="B80" s="94" t="n"/>
-      <c r="C80" s="94" t="n"/>
+    <row r="80" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A80" s="60" t="n"/>
+      <c r="B80" s="63" t="n"/>
+      <c r="C80" s="63" t="n"/>
       <c r="D80" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -18532,16 +18427,16 @@
       <c r="U80" s="28" t="n"/>
       <c r="V80" s="29" t="n"/>
     </row>
-    <row r="81" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A81" s="89" t="n">
+    <row r="81" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A81" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="B81" s="90" t="inlineStr">
+      <c r="B81" s="61" t="inlineStr">
         <is>
           <t>정성욱</t>
         </is>
       </c>
-      <c r="C81" s="90" t="n">
+      <c r="C81" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -18598,10 +18493,10 @@
       <c r="U81" s="23" t="n"/>
       <c r="V81" s="23" t="n"/>
     </row>
-    <row r="82" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A82" s="91" t="n"/>
-      <c r="B82" s="92" t="n"/>
-      <c r="C82" s="92" t="n"/>
+    <row r="82" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A82" s="59" t="n"/>
+      <c r="B82" s="62" t="n"/>
+      <c r="C82" s="62" t="n"/>
       <c r="D82" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -18656,10 +18551,10 @@
       <c r="U82" s="23" t="n"/>
       <c r="V82" s="23" t="n"/>
     </row>
-    <row r="83" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A83" s="91" t="n"/>
-      <c r="B83" s="92" t="n"/>
-      <c r="C83" s="92" t="n"/>
+    <row r="83" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A83" s="59" t="n"/>
+      <c r="B83" s="62" t="n"/>
+      <c r="C83" s="62" t="n"/>
       <c r="D83" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -18714,10 +18609,10 @@
       <c r="U83" s="23" t="n"/>
       <c r="V83" s="23" t="n"/>
     </row>
-    <row r="84" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A84" s="91" t="n"/>
-      <c r="B84" s="92" t="n"/>
-      <c r="C84" s="92" t="n"/>
+    <row r="84" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A84" s="59" t="n"/>
+      <c r="B84" s="62" t="n"/>
+      <c r="C84" s="62" t="n"/>
       <c r="D84" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -18772,10 +18667,10 @@
       <c r="U84" s="23" t="n"/>
       <c r="V84" s="23" t="n"/>
     </row>
-    <row r="85" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A85" s="91" t="n"/>
-      <c r="B85" s="92" t="n"/>
-      <c r="C85" s="92" t="n"/>
+    <row r="85" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A85" s="59" t="n"/>
+      <c r="B85" s="62" t="n"/>
+      <c r="C85" s="62" t="n"/>
       <c r="D85" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -18830,10 +18725,10 @@
       <c r="U85" s="23" t="n"/>
       <c r="V85" s="23" t="n"/>
     </row>
-    <row r="86" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A86" s="93" t="n"/>
-      <c r="B86" s="94" t="n"/>
-      <c r="C86" s="94" t="n"/>
+    <row r="86" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A86" s="60" t="n"/>
+      <c r="B86" s="63" t="n"/>
+      <c r="C86" s="63" t="n"/>
       <c r="D86" s="25" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -18888,16 +18783,16 @@
       <c r="U86" s="28" t="n"/>
       <c r="V86" s="28" t="n"/>
     </row>
-    <row r="87" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A87" s="89" t="n">
+    <row r="87" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A87" s="58" t="n">
         <v>15</v>
       </c>
-      <c r="B87" s="90" t="inlineStr">
+      <c r="B87" s="61" t="inlineStr">
         <is>
           <t>김태영</t>
         </is>
       </c>
-      <c r="C87" s="90" t="n">
+      <c r="C87" s="61" t="n">
         <v>7</v>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -18954,10 +18849,10 @@
       <c r="U87" s="23" t="n"/>
       <c r="V87" s="24" t="n"/>
     </row>
-    <row r="88" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A88" s="91" t="n"/>
-      <c r="B88" s="92" t="n"/>
-      <c r="C88" s="92" t="n"/>
+    <row r="88" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A88" s="59" t="n"/>
+      <c r="B88" s="62" t="n"/>
+      <c r="C88" s="62" t="n"/>
       <c r="D88" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -19012,10 +18907,10 @@
       <c r="U88" s="23" t="n"/>
       <c r="V88" s="24" t="n"/>
     </row>
-    <row r="89" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A89" s="91" t="n"/>
-      <c r="B89" s="92" t="n"/>
-      <c r="C89" s="92" t="n"/>
+    <row r="89" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A89" s="59" t="n"/>
+      <c r="B89" s="62" t="n"/>
+      <c r="C89" s="62" t="n"/>
       <c r="D89" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19070,10 +18965,10 @@
       <c r="U89" s="23" t="n"/>
       <c r="V89" s="24" t="n"/>
     </row>
-    <row r="90" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A90" s="91" t="n"/>
-      <c r="B90" s="92" t="n"/>
-      <c r="C90" s="92" t="n"/>
+    <row r="90" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A90" s="59" t="n"/>
+      <c r="B90" s="62" t="n"/>
+      <c r="C90" s="62" t="n"/>
       <c r="D90" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -19128,10 +19023,10 @@
       <c r="U90" s="23" t="n"/>
       <c r="V90" s="24" t="n"/>
     </row>
-    <row r="91" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A91" s="91" t="n"/>
-      <c r="B91" s="92" t="n"/>
-      <c r="C91" s="92" t="n"/>
+    <row r="91" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A91" s="59" t="n"/>
+      <c r="B91" s="62" t="n"/>
+      <c r="C91" s="62" t="n"/>
       <c r="D91" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19186,10 +19081,10 @@
       <c r="U91" s="23" t="n"/>
       <c r="V91" s="24" t="n"/>
     </row>
-    <row r="92" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A92" s="91" t="n"/>
-      <c r="B92" s="92" t="n"/>
-      <c r="C92" s="92" t="n"/>
+    <row r="92" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A92" s="59" t="n"/>
+      <c r="B92" s="62" t="n"/>
+      <c r="C92" s="62" t="n"/>
       <c r="D92" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19244,10 +19139,10 @@
       <c r="U92" s="23" t="n"/>
       <c r="V92" s="24" t="n"/>
     </row>
-    <row r="93" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A93" s="93" t="n"/>
-      <c r="B93" s="94" t="n"/>
-      <c r="C93" s="94" t="n"/>
+    <row r="93" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A93" s="60" t="n"/>
+      <c r="B93" s="63" t="n"/>
+      <c r="C93" s="63" t="n"/>
       <c r="D93" s="25" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -19302,16 +19197,16 @@
       <c r="U93" s="28" t="n"/>
       <c r="V93" s="29" t="n"/>
     </row>
-    <row r="94" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A94" s="89" t="n">
+    <row r="94" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A94" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="B94" s="90" t="inlineStr">
+      <c r="B94" s="61" t="inlineStr">
         <is>
           <t>양영선</t>
         </is>
       </c>
-      <c r="C94" s="90" t="n">
+      <c r="C94" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D94" s="36" t="inlineStr">
@@ -19364,10 +19259,10 @@
       <c r="U94" s="23" t="n"/>
       <c r="V94" s="24" t="n"/>
     </row>
-    <row r="95" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A95" s="91" t="n"/>
-      <c r="B95" s="92" t="n"/>
-      <c r="C95" s="92" t="n"/>
+    <row r="95" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A95" s="59" t="n"/>
+      <c r="B95" s="62" t="n"/>
+      <c r="C95" s="62" t="n"/>
       <c r="D95" s="36" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -19418,10 +19313,10 @@
       <c r="U95" s="23" t="n"/>
       <c r="V95" s="24" t="n"/>
     </row>
-    <row r="96" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A96" s="91" t="n"/>
-      <c r="B96" s="92" t="n"/>
-      <c r="C96" s="92" t="n"/>
+    <row r="96" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A96" s="59" t="n"/>
+      <c r="B96" s="62" t="n"/>
+      <c r="C96" s="62" t="n"/>
       <c r="D96" s="36" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19472,10 +19367,10 @@
       <c r="U96" s="23" t="n"/>
       <c r="V96" s="24" t="n"/>
     </row>
-    <row r="97" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A97" s="91" t="n"/>
-      <c r="B97" s="92" t="n"/>
-      <c r="C97" s="92" t="n"/>
+    <row r="97" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A97" s="59" t="n"/>
+      <c r="B97" s="62" t="n"/>
+      <c r="C97" s="62" t="n"/>
       <c r="D97" s="36" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -19526,10 +19421,10 @@
       <c r="U97" s="23" t="n"/>
       <c r="V97" s="24" t="n"/>
     </row>
-    <row r="98" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A98" s="93" t="n"/>
-      <c r="B98" s="94" t="n"/>
-      <c r="C98" s="94" t="n"/>
+    <row r="98" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A98" s="60" t="n"/>
+      <c r="B98" s="63" t="n"/>
+      <c r="C98" s="63" t="n"/>
       <c r="D98" s="56" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19580,16 +19475,16 @@
       <c r="U98" s="28" t="n"/>
       <c r="V98" s="29" t="n"/>
     </row>
-    <row r="99" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A99" s="89" t="n">
+    <row r="99" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A99" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="90" t="inlineStr">
+      <c r="B99" s="61" t="inlineStr">
         <is>
           <t>장진석</t>
         </is>
       </c>
-      <c r="C99" s="90" t="n">
+      <c r="C99" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -19642,10 +19537,10 @@
       <c r="U99" s="23" t="n"/>
       <c r="V99" s="24" t="n"/>
     </row>
-    <row r="100" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A100" s="91" t="n"/>
-      <c r="B100" s="92" t="n"/>
-      <c r="C100" s="92" t="n"/>
+    <row r="100" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A100" s="59" t="n"/>
+      <c r="B100" s="62" t="n"/>
+      <c r="C100" s="62" t="n"/>
       <c r="D100" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19696,10 +19591,10 @@
       <c r="U100" s="23" t="n"/>
       <c r="V100" s="24" t="n"/>
     </row>
-    <row r="101" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A101" s="91" t="n"/>
-      <c r="B101" s="92" t="n"/>
-      <c r="C101" s="92" t="n"/>
+    <row r="101" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A101" s="59" t="n"/>
+      <c r="B101" s="62" t="n"/>
+      <c r="C101" s="62" t="n"/>
       <c r="D101" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -19750,10 +19645,10 @@
       <c r="U101" s="23" t="n"/>
       <c r="V101" s="24" t="n"/>
     </row>
-    <row r="102" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A102" s="91" t="n"/>
-      <c r="B102" s="92" t="n"/>
-      <c r="C102" s="92" t="n"/>
+    <row r="102" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A102" s="59" t="n"/>
+      <c r="B102" s="62" t="n"/>
+      <c r="C102" s="62" t="n"/>
       <c r="D102" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -19804,10 +19699,10 @@
       <c r="U102" s="23" t="n"/>
       <c r="V102" s="24" t="n"/>
     </row>
-    <row r="103" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A103" s="91" t="n"/>
-      <c r="B103" s="92" t="n"/>
-      <c r="C103" s="92" t="n"/>
+    <row r="103" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A103" s="59" t="n"/>
+      <c r="B103" s="62" t="n"/>
+      <c r="C103" s="62" t="n"/>
       <c r="D103" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -19858,10 +19753,10 @@
       <c r="U103" s="23" t="n"/>
       <c r="V103" s="24" t="n"/>
     </row>
-    <row r="104" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A104" s="93" t="n"/>
-      <c r="B104" s="94" t="n"/>
-      <c r="C104" s="94" t="n"/>
+    <row r="104" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A104" s="60" t="n"/>
+      <c r="B104" s="63" t="n"/>
+      <c r="C104" s="63" t="n"/>
       <c r="D104" s="25" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -19912,16 +19807,16 @@
       <c r="U104" s="28" t="n"/>
       <c r="V104" s="29" t="n"/>
     </row>
-    <row r="105" ht="51" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A105" s="89" t="n">
+    <row r="105" ht="51" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A105" s="58" t="n">
         <v>18</v>
       </c>
-      <c r="B105" s="90" t="inlineStr">
+      <c r="B105" s="61" t="inlineStr">
         <is>
           <t>김민채</t>
         </is>
       </c>
-      <c r="C105" s="90" t="n">
+      <c r="C105" s="61" t="n">
         <v>7</v>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -19978,10 +19873,10 @@
       <c r="U105" s="23" t="n"/>
       <c r="V105" s="24" t="n"/>
     </row>
-    <row r="106" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A106" s="91" t="n"/>
-      <c r="B106" s="92" t="n"/>
-      <c r="C106" s="92" t="n"/>
+    <row r="106" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A106" s="59" t="n"/>
+      <c r="B106" s="62" t="n"/>
+      <c r="C106" s="62" t="n"/>
       <c r="D106" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -20036,10 +19931,10 @@
       <c r="U106" s="23" t="n"/>
       <c r="V106" s="24" t="n"/>
     </row>
-    <row r="107" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A107" s="91" t="n"/>
-      <c r="B107" s="92" t="n"/>
-      <c r="C107" s="92" t="n"/>
+    <row r="107" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A107" s="59" t="n"/>
+      <c r="B107" s="62" t="n"/>
+      <c r="C107" s="62" t="n"/>
       <c r="D107" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -20094,10 +19989,10 @@
       <c r="U107" s="23" t="n"/>
       <c r="V107" s="30" t="n"/>
     </row>
-    <row r="108" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A108" s="91" t="n"/>
-      <c r="B108" s="92" t="n"/>
-      <c r="C108" s="92" t="n"/>
+    <row r="108" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A108" s="59" t="n"/>
+      <c r="B108" s="62" t="n"/>
+      <c r="C108" s="62" t="n"/>
       <c r="D108" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -20152,10 +20047,10 @@
       <c r="U108" s="23" t="n"/>
       <c r="V108" s="30" t="n"/>
     </row>
-    <row r="109" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A109" s="91" t="n"/>
-      <c r="B109" s="92" t="n"/>
-      <c r="C109" s="92" t="n"/>
+    <row r="109" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A109" s="59" t="n"/>
+      <c r="B109" s="62" t="n"/>
+      <c r="C109" s="62" t="n"/>
       <c r="D109" s="20" t="inlineStr">
         <is>
           <t>4 회</t>
@@ -20210,10 +20105,10 @@
       <c r="U109" s="23" t="n"/>
       <c r="V109" s="30" t="n"/>
     </row>
-    <row r="110" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A110" s="91" t="n"/>
-      <c r="B110" s="92" t="n"/>
-      <c r="C110" s="92" t="n"/>
+    <row r="110" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A110" s="59" t="n"/>
+      <c r="B110" s="62" t="n"/>
+      <c r="C110" s="62" t="n"/>
       <c r="D110" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -20268,10 +20163,10 @@
       <c r="U110" s="23" t="n"/>
       <c r="V110" s="30" t="n"/>
     </row>
-    <row r="111" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A111" s="93" t="n"/>
-      <c r="B111" s="94" t="n"/>
-      <c r="C111" s="94" t="n"/>
+    <row r="111" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A111" s="60" t="n"/>
+      <c r="B111" s="63" t="n"/>
+      <c r="C111" s="63" t="n"/>
       <c r="D111" s="25" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -20326,16 +20221,16 @@
       <c r="U111" s="28" t="n"/>
       <c r="V111" s="29" t="n"/>
     </row>
-    <row r="112" ht="50.25" customHeight="1" s="80" thickBot="1" thickTop="1">
-      <c r="A112" s="89" t="n">
+    <row r="112" ht="50.25" customHeight="1" s="73" thickBot="1" thickTop="1">
+      <c r="A112" s="58" t="n">
         <v>19</v>
       </c>
-      <c r="B112" s="90" t="inlineStr">
+      <c r="B112" s="61" t="inlineStr">
         <is>
           <t>황미옥</t>
         </is>
       </c>
-      <c r="C112" s="90" t="n">
+      <c r="C112" s="61" t="n">
         <v>7</v>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -20392,10 +20287,10 @@
       <c r="U112" s="23" t="n"/>
       <c r="V112" s="24" t="n"/>
     </row>
-    <row r="113" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A113" s="91" t="n"/>
-      <c r="B113" s="92" t="n"/>
-      <c r="C113" s="92" t="n"/>
+    <row r="113" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A113" s="59" t="n"/>
+      <c r="B113" s="62" t="n"/>
+      <c r="C113" s="62" t="n"/>
       <c r="D113" s="20" t="inlineStr">
         <is>
           <t>3 회</t>
@@ -20450,10 +20345,10 @@
       <c r="U113" s="23" t="n"/>
       <c r="V113" s="24" t="n"/>
     </row>
-    <row r="114" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A114" s="91" t="n"/>
-      <c r="B114" s="92" t="n"/>
-      <c r="C114" s="92" t="n"/>
+    <row r="114" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A114" s="59" t="n"/>
+      <c r="B114" s="62" t="n"/>
+      <c r="C114" s="62" t="n"/>
       <c r="D114" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -20508,10 +20403,10 @@
       <c r="U114" s="23" t="n"/>
       <c r="V114" s="24" t="n"/>
     </row>
-    <row r="115" ht="51" customHeight="1" s="80" thickBot="1">
-      <c r="A115" s="91" t="n"/>
-      <c r="B115" s="92" t="n"/>
-      <c r="C115" s="92" t="n"/>
+    <row r="115" ht="51" customHeight="1" s="73" thickBot="1">
+      <c r="A115" s="59" t="n"/>
+      <c r="B115" s="62" t="n"/>
+      <c r="C115" s="62" t="n"/>
       <c r="D115" s="20" t="inlineStr">
         <is>
           <t>7 회</t>
@@ -20566,10 +20461,10 @@
       <c r="U115" s="23" t="n"/>
       <c r="V115" s="24" t="n"/>
     </row>
-    <row r="116" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A116" s="91" t="n"/>
-      <c r="B116" s="92" t="n"/>
-      <c r="C116" s="92" t="n"/>
+    <row r="116" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A116" s="59" t="n"/>
+      <c r="B116" s="62" t="n"/>
+      <c r="C116" s="62" t="n"/>
       <c r="D116" s="20" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -20624,10 +20519,10 @@
       <c r="U116" s="23" t="n"/>
       <c r="V116" s="24" t="n"/>
     </row>
-    <row r="117" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A117" s="91" t="n"/>
-      <c r="B117" s="92" t="n"/>
-      <c r="C117" s="92" t="n"/>
+    <row r="117" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A117" s="59" t="n"/>
+      <c r="B117" s="62" t="n"/>
+      <c r="C117" s="62" t="n"/>
       <c r="D117" s="20" t="inlineStr">
         <is>
           <t>1 회</t>
@@ -20682,10 +20577,10 @@
       <c r="U117" s="23" t="n"/>
       <c r="V117" s="24" t="n"/>
     </row>
-    <row r="118" ht="50.25" customHeight="1" s="80" thickBot="1">
-      <c r="A118" s="93" t="n"/>
-      <c r="B118" s="94" t="n"/>
-      <c r="C118" s="94" t="n"/>
+    <row r="118" ht="50.25" customHeight="1" s="73" thickBot="1">
+      <c r="A118" s="60" t="n"/>
+      <c r="B118" s="63" t="n"/>
+      <c r="C118" s="63" t="n"/>
       <c r="D118" s="25" t="inlineStr">
         <is>
           <t>2 회</t>
@@ -20740,8 +20635,8 @@
       <c r="U118" s="28" t="n"/>
       <c r="V118" s="29" t="n"/>
     </row>
-    <row r="119" ht="50.25" customHeight="1" s="80" thickTop="1"/>
-    <row r="120" ht="17.25" customHeight="1" s="80"/>
+    <row r="119" ht="50.25" customHeight="1" s="73" thickTop="1"/>
+    <row r="120" ht="17.25" customHeight="1" s="73"/>
   </sheetData>
   <mergeCells count="62">
     <mergeCell ref="A87:A93"/>
